--- a/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5755852889762161</v>
+        <v>0.6579246446791172</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1511705779524322</v>
+        <v>0.3158492893582343</v>
       </c>
       <c r="F2" t="n">
-        <v>1.356185999273623</v>
+        <v>1.92333248930474</v>
       </c>
       <c r="G2" t="n">
-        <v>0.199</v>
+        <v>0.044</v>
       </c>
       <c r="H2" t="n">
-        <v>190.6934098998242</v>
+        <v>3.114047681002716</v>
       </c>
       <c r="I2" t="n">
-        <v>331.3034810861955</v>
+        <v>4.733137307117441</v>
       </c>
       <c r="J2" t="n">
-        <v>8.294327430324568</v>
+        <v>0.1606192465262189</v>
       </c>
       <c r="K2" t="n">
-        <v>3.164911547250205</v>
+        <v>2.381742084341708</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5256219687263319</v>
+        <v>0.3532165705482233</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2884329530894979</v>
+        <v>0.02982485582233496</v>
       </c>
       <c r="F3" t="n">
-        <v>2.216046840597059</v>
+        <v>1.092225169861308</v>
       </c>
       <c r="G3" t="n">
-        <v>0.005</v>
+        <v>0.375</v>
       </c>
       <c r="H3" t="n">
-        <v>254.0846707058953</v>
+        <v>2.642463890044155</v>
       </c>
       <c r="I3" t="n">
-        <v>483.3981184644624</v>
+        <v>7.481143610965981</v>
       </c>
       <c r="J3" t="n">
-        <v>10.25014890180989</v>
+        <v>0.1120830378775509</v>
       </c>
       <c r="K3" t="n">
-        <v>2.903559191605957</v>
+        <v>1.557899137099524</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4240549598658215</v>
+        <v>0.2854385399915653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2183603026750435</v>
+        <v>0.03023801855998143</v>
       </c>
       <c r="F4" t="n">
-        <v>2.061574985258456</v>
+        <v>1.11848729144579</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004</v>
+        <v>0.335</v>
       </c>
       <c r="H4" t="n">
-        <v>262.0799181803197</v>
+        <v>2.788326491281801</v>
       </c>
       <c r="I4" t="n">
-        <v>618.0329037142883</v>
+        <v>9.768570464815983</v>
       </c>
       <c r="J4" t="n">
-        <v>8.532316708043748</v>
+        <v>0.09405825759349087</v>
       </c>
       <c r="K4" t="n">
-        <v>2.097546186872141</v>
+        <v>1.534762566826719</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3430968682153295</v>
+        <v>0.3388689749504772</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1702276230088373</v>
+        <v>0.1648871262532344</v>
       </c>
       <c r="F5" t="n">
-        <v>1.984718957993369</v>
+        <v>1.947726027099327</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="H5" t="n">
-        <v>248.3873571825596</v>
+        <v>4.350238375964505</v>
       </c>
       <c r="I5" t="n">
-        <v>723.9569351786397</v>
+        <v>12.83752334246667</v>
       </c>
       <c r="J5" t="n">
-        <v>6.183664494146667</v>
+        <v>0.1435024146267186</v>
       </c>
       <c r="K5" t="n">
-        <v>1.525498552217103</v>
+        <v>1.760964712626336</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.340561546193754</v>
+        <v>0.3782934230417848</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2031785349841193</v>
+        <v>0.2487712195088234</v>
       </c>
       <c r="F6" t="n">
-        <v>2.478920378838446</v>
+        <v>2.920683965552784</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H6" t="n">
-        <v>311.3986155603587</v>
+        <v>5.773036539918646</v>
       </c>
       <c r="I6" t="n">
-        <v>914.3681047982918</v>
+        <v>15.26073726975946</v>
       </c>
       <c r="J6" t="n">
-        <v>7.388694435646972</v>
+        <v>0.1705300806849534</v>
       </c>
       <c r="K6" t="n">
-        <v>1.682124973582259</v>
+        <v>1.744503813007251</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2817620862995145</v>
+        <v>0.2835613744606992</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1535053159958564</v>
+        <v>0.1556259056143955</v>
       </c>
       <c r="F7" t="n">
-        <v>2.196859359801594</v>
+        <v>2.216440655729005</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H7" t="n">
-        <v>290.3417616227973</v>
+        <v>4.835100485385633</v>
       </c>
       <c r="I7" t="n">
-        <v>1030.450070255948</v>
+        <v>17.05133675057625</v>
       </c>
       <c r="J7" t="n">
-        <v>5.828707214872598</v>
+        <v>0.1248407465431917</v>
       </c>
       <c r="K7" t="n">
-        <v>1.678016973261818</v>
+        <v>1.849272288296433</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2551292489076615</v>
+        <v>0.2472077078854155</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1422700441967011</v>
+        <v>0.1331482696862359</v>
       </c>
       <c r="F8" t="n">
-        <v>2.260597614178337</v>
+        <v>2.167358631503358</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0.011</v>
       </c>
       <c r="H8" t="n">
-        <v>296.592055524509</v>
+        <v>4.709947937837544</v>
       </c>
       <c r="I8" t="n">
-        <v>1162.51686858473</v>
+        <v>19.05259337633872</v>
       </c>
       <c r="J8" t="n">
-        <v>5.705509415246404</v>
+        <v>0.1033030968368027</v>
       </c>
       <c r="K8" t="n">
-        <v>1.621718484046386</v>
+        <v>2.001450672305995</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2600434908304279</v>
+        <v>0.25094837548363</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1626807922554842</v>
+        <v>0.1523889512051603</v>
       </c>
       <c r="F9" t="n">
-        <v>2.670873903831483</v>
+        <v>2.546163163195847</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>340.5974270481971</v>
+        <v>5.236189817651347</v>
       </c>
       <c r="I9" t="n">
-        <v>1309.77101545794</v>
+        <v>20.86560555556542</v>
       </c>
       <c r="J9" t="n">
-        <v>6.079869406982933</v>
+        <v>0.08398596201227704</v>
       </c>
       <c r="K9" t="n">
-        <v>1.614194583864673</v>
+        <v>1.525801098174523</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2958595079622759</v>
+        <v>0.2751480018178623</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2120332589101659</v>
+        <v>0.1888560972723696</v>
       </c>
       <c r="F10" t="n">
-        <v>3.529437512805292</v>
+        <v>3.188572592841613</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>436.2145161079187</v>
+        <v>6.132228811762252</v>
       </c>
       <c r="I10" t="n">
-        <v>1474.397490593876</v>
+        <v>22.28701924508817</v>
       </c>
       <c r="J10" t="n">
-        <v>7.515089085891447</v>
+        <v>0.09493454891279297</v>
       </c>
       <c r="K10" t="n">
-        <v>1.532079522297151</v>
+        <v>1.50230557236947</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2860611958570173</v>
+        <v>0.268282848947674</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2101102592460616</v>
+        <v>0.1904405988357245</v>
       </c>
       <c r="F11" t="n">
-        <v>3.766394578151314</v>
+        <v>3.446494012722404</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>448.231841485375</v>
+        <v>6.728530441155329</v>
       </c>
       <c r="I11" t="n">
-        <v>1566.908927100395</v>
+        <v>25.07998728784807</v>
       </c>
       <c r="J11" t="n">
-        <v>7.188244463959996</v>
+        <v>0.1014832360555909</v>
       </c>
       <c r="K11" t="n">
-        <v>1.511169518691759</v>
+        <v>1.49146893192355</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2893160670625271</v>
+        <v>0.2823756878403189</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2209810735108469</v>
+        <v>0.2133733501326571</v>
       </c>
       <c r="F12" t="n">
-        <v>4.233790800663854</v>
+        <v>4.092262627922032</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>498.1335897537966</v>
+        <v>7.642427025733995</v>
       </c>
       <c r="I12" t="n">
-        <v>1721.762620415201</v>
+        <v>27.06474868351884</v>
       </c>
       <c r="J12" t="n">
-        <v>7.39451424108094</v>
+        <v>0.1117924196474495</v>
       </c>
       <c r="K12" t="n">
-        <v>1.574366151002452</v>
+        <v>1.395266770664399</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2794460989117294</v>
+        <v>0.2858918673242215</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2151109291717054</v>
+        <v>0.222132212621027</v>
       </c>
       <c r="F13" t="n">
-        <v>4.343597755954636</v>
+        <v>4.483899240908181</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>506.8889733138347</v>
+        <v>8.152648019882438</v>
       </c>
       <c r="I13" t="n">
-        <v>1813.906063773498</v>
+        <v>28.51654402129866</v>
       </c>
       <c r="J13" t="n">
-        <v>7.070405377868616</v>
+        <v>0.1074578215631683</v>
       </c>
       <c r="K13" t="n">
-        <v>1.565287016338877</v>
+        <v>1.376403804581479</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2662099333705267</v>
+        <v>0.2703096282531469</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2060632065976191</v>
+        <v>0.2104989420443883</v>
       </c>
       <c r="F14" t="n">
-        <v>4.426008656724401</v>
+        <v>4.519420280678266</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>520.0013463685016</v>
+        <v>8.715299936248677</v>
       </c>
       <c r="I14" t="n">
-        <v>1953.350649935113</v>
+        <v>32.24191455025323</v>
       </c>
       <c r="J14" t="n">
-        <v>6.638738296098127</v>
+        <v>0.1020266758586354</v>
       </c>
       <c r="K14" t="n">
-        <v>1.590247177586034</v>
+        <v>1.340574768793374</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2346826155705927</v>
+        <v>0.264554337661392</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1767040258410921</v>
+        <v>0.2088387571811944</v>
       </c>
       <c r="F15" t="n">
-        <v>4.047746188127475</v>
+        <v>4.748300841187857</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>486.4548087603556</v>
+        <v>9.198312212603732</v>
       </c>
       <c r="I15" t="n">
-        <v>2072.819955485922</v>
+        <v>34.7690848462928</v>
       </c>
       <c r="J15" t="n">
-        <v>5.839829976999308</v>
+        <v>0.1043199963201647</v>
       </c>
       <c r="K15" t="n">
-        <v>1.550158115843763</v>
+        <v>1.394029296786374</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2323611456709233</v>
+        <v>0.2548527473464362</v>
       </c>
       <c r="E16" t="n">
-        <v>0.177529798933132</v>
+        <v>0.2016279435854673</v>
       </c>
       <c r="F16" t="n">
-        <v>4.237742814928417</v>
+        <v>4.788232728691174</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>496.2224308025014</v>
+        <v>9.214223689832377</v>
       </c>
       <c r="I16" t="n">
-        <v>2135.565433582714</v>
+        <v>36.15508871602214</v>
       </c>
       <c r="J16" t="n">
-        <v>5.669571852455068</v>
+        <v>0.09960781211974495</v>
       </c>
       <c r="K16" t="n">
-        <v>1.530918918469592</v>
+        <v>1.36021395748662</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2324913222434055</v>
+        <v>0.270570616271733</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1813240770596326</v>
+        <v>0.2219419906898485</v>
       </c>
       <c r="F17" t="n">
-        <v>4.543752969470733</v>
+        <v>5.564019402854107</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>525.9191440067972</v>
+        <v>10.49480561146374</v>
       </c>
       <c r="I17" t="n">
-        <v>2262.102253675468</v>
+        <v>38.78767678499075</v>
       </c>
       <c r="J17" t="n">
-        <v>5.725451480651323</v>
+        <v>0.1059045920777064</v>
       </c>
       <c r="K17" t="n">
-        <v>1.40808854614921</v>
+        <v>1.320372237737873</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2329768550408527</v>
+        <v>0.2585272602203122</v>
       </c>
       <c r="E18" t="n">
-        <v>0.185037908480906</v>
+        <v>0.2121852139840816</v>
       </c>
       <c r="F18" t="n">
-        <v>4.859865970344584</v>
+        <v>5.578675980392816</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>545.972936970958</v>
+        <v>10.81576955772907</v>
       </c>
       <c r="I18" t="n">
-        <v>2343.464276205554</v>
+        <v>41.83608934899969</v>
       </c>
       <c r="J18" t="n">
-        <v>5.56404160714597</v>
+        <v>0.1035069240624528</v>
       </c>
       <c r="K18" t="n">
-        <v>1.356354738537741</v>
+        <v>1.307941320700577</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2224747594224214</v>
+        <v>0.2381634173472308</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1761934951023274</v>
+        <v>0.1928160017131375</v>
       </c>
       <c r="F19" t="n">
-        <v>4.807015596715869</v>
+        <v>5.251973326748378</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>550.5707756198965</v>
+        <v>10.4180269885074</v>
       </c>
       <c r="I19" t="n">
-        <v>2474.756134355478</v>
+        <v>43.74318736499491</v>
       </c>
       <c r="J19" t="n">
-        <v>5.246150758657543</v>
+        <v>0.09985274334431969</v>
       </c>
       <c r="K19" t="n">
-        <v>1.298901057751075</v>
+        <v>1.285074598382898</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2279835395489321</v>
+        <v>0.2370518653525321</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1846118282876361</v>
+        <v>0.1941896105970564</v>
       </c>
       <c r="F20" t="n">
-        <v>5.256503211861509</v>
+        <v>5.530550520612738</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>591.9513970181724</v>
+        <v>10.9014284561925</v>
       </c>
       <c r="I20" t="n">
-        <v>2596.465508822938</v>
+        <v>45.98752446001815</v>
       </c>
       <c r="J20" t="n">
-        <v>5.353943655071082</v>
+        <v>0.09973109849735637</v>
       </c>
       <c r="K20" t="n">
-        <v>1.309683525488907</v>
+        <v>1.29015848663695</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2141315808957043</v>
+        <v>0.2214800836835681</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1723300692412205</v>
+        <v>0.1800694498369494</v>
       </c>
       <c r="F21" t="n">
-        <v>5.122579840309091</v>
+        <v>5.348386709170176</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>584.9491316892037</v>
+        <v>10.62592711522805</v>
       </c>
       <c r="I21" t="n">
-        <v>2731.727516522241</v>
+        <v>47.97689678684369</v>
       </c>
       <c r="J21" t="n">
-        <v>4.985494666598608</v>
+        <v>0.09053605556362303</v>
       </c>
       <c r="K21" t="n">
-        <v>1.304201885230548</v>
+        <v>1.2364679451503</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2232963412792219</v>
+        <v>0.2081966501944755</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1836686035893864</v>
+        <v>0.167798520102357</v>
       </c>
       <c r="F22" t="n">
-        <v>5.634849585079812</v>
+        <v>5.153620965122173</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>635.678056637066</v>
+        <v>10.49266200544291</v>
       </c>
       <c r="I22" t="n">
-        <v>2846.791187868947</v>
+        <v>50.39784259565064</v>
       </c>
       <c r="J22" t="n">
-        <v>5.342279290739278</v>
+        <v>0.0886657657222833</v>
       </c>
       <c r="K22" t="n">
-        <v>1.339881415802044</v>
+        <v>1.225172581294342</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.218517480938215</v>
+        <v>0.203265281032049</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1805814363235654</v>
+        <v>0.1645888383637019</v>
       </c>
       <c r="F23" t="n">
-        <v>5.760154574834883</v>
+        <v>5.255531972654808</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>655.3893111570941</v>
+        <v>10.5266299300827</v>
       </c>
       <c r="I23" t="n">
-        <v>2999.253461751203</v>
+        <v>51.78764359872631</v>
       </c>
       <c r="J23" t="n">
-        <v>5.299448413396808</v>
+        <v>0.0842502170661563</v>
       </c>
       <c r="K23" t="n">
-        <v>1.33931270710166</v>
+        <v>1.207949575491007</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2208582366458279</v>
+        <v>0.1952250522206383</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1847868587127645</v>
+        <v>0.1579669527864085</v>
       </c>
       <c r="F24" t="n">
-        <v>6.122811195504292</v>
+        <v>5.239801685678079</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>705.6293275768201</v>
+        <v>10.70426964850156</v>
       </c>
       <c r="I24" t="n">
-        <v>3194.942322700781</v>
+        <v>54.83040996400337</v>
       </c>
       <c r="J24" t="n">
-        <v>5.398015944144062</v>
+        <v>0.08164509905794252</v>
       </c>
       <c r="K24" t="n">
-        <v>1.327543610861364</v>
+        <v>1.204524834043881</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2061241458806004</v>
+        <v>0.1864957273733484</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1706832595359843</v>
+        <v>0.1501785723453728</v>
       </c>
       <c r="F25" t="n">
-        <v>5.81599861460331</v>
+        <v>5.135196499552032</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>678.813285877826</v>
+        <v>10.61666405428146</v>
       </c>
       <c r="I25" t="n">
-        <v>3293.225463605006</v>
+        <v>56.92711679677149</v>
       </c>
       <c r="J25" t="n">
-        <v>4.96046172336269</v>
+        <v>0.07757914103192969</v>
       </c>
       <c r="K25" t="n">
-        <v>1.283691461591087</v>
+        <v>1.206635847824345</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2031645653783596</v>
+        <v>0.1715280714912285</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1691117690270074</v>
+        <v>0.1361232882216228</v>
       </c>
       <c r="F26" t="n">
-        <v>5.966163932093421</v>
+        <v>4.844771119909164</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>689.9503162673095</v>
+        <v>10.21142681261125</v>
       </c>
       <c r="I26" t="n">
-        <v>3396.016992345067</v>
+        <v>59.53210296038012</v>
       </c>
       <c r="J26" t="n">
-        <v>4.853376658121163</v>
+        <v>0.07136987377933823</v>
       </c>
       <c r="K26" t="n">
-        <v>1.279764145112816</v>
+        <v>1.205472488895055</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1918685918658</v>
+        <v>0.1668907619510709</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1587484521881689</v>
+        <v>0.1327469407195575</v>
       </c>
       <c r="F27" t="n">
-        <v>5.793109380978402</v>
+        <v>4.887875929863316</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>676.0836276193368</v>
+        <v>10.28660837487032</v>
       </c>
       <c r="I27" t="n">
-        <v>3523.680562018274</v>
+        <v>61.63677518523258</v>
       </c>
       <c r="J27" t="n">
-        <v>4.492789531176008</v>
+        <v>0.06943400515022734</v>
       </c>
       <c r="K27" t="n">
-        <v>1.250343054841244</v>
+        <v>1.205057379429636</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1912461827455565</v>
+        <v>0.1649545051665424</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1591527772989515</v>
+        <v>0.1318177791810877</v>
       </c>
       <c r="F28" t="n">
-        <v>5.95904922161472</v>
+        <v>4.977996475540433</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>697.0485726523987</v>
+        <v>10.40719989779272</v>
       </c>
       <c r="I28" t="n">
-        <v>3644.77116690892</v>
+        <v>63.09133471247323</v>
       </c>
       <c r="J28" t="n">
-        <v>4.512053297405025</v>
+        <v>0.06752476146362883</v>
       </c>
       <c r="K28" t="n">
-        <v>1.233514112639437</v>
+        <v>1.201785134710402</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1837642497820643</v>
+        <v>0.1575879160011046</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1526102135142042</v>
+        <v>0.1254347830240476</v>
       </c>
       <c r="F29" t="n">
-        <v>5.898569552980956</v>
+        <v>4.901168297147024</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>692.1452534146138</v>
+        <v>10.27880607570618</v>
       </c>
       <c r="I29" t="n">
-        <v>3766.484799058931</v>
+        <v>65.22585193419354</v>
       </c>
       <c r="J29" t="n">
-        <v>4.283247081278819</v>
+        <v>0.06362453768365349</v>
       </c>
       <c r="K29" t="n">
-        <v>1.193834075731905</v>
+        <v>1.238134139596283</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1788636025916061</v>
+        <v>0.1541419101105417</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1486747644515916</v>
+        <v>0.1230441862175468</v>
       </c>
       <c r="F30" t="n">
-        <v>5.924825651190841</v>
+        <v>4.956694279006841</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>690.6982062168765</v>
+        <v>10.2839394812705</v>
       </c>
       <c r="I30" t="n">
-        <v>3861.591716867779</v>
+        <v>66.7173481494777</v>
       </c>
       <c r="J30" t="n">
-        <v>4.08818912868891</v>
+        <v>0.06114830129389158</v>
       </c>
       <c r="K30" t="n">
-        <v>1.199402691513161</v>
+        <v>1.235652207029463</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1742823078008449</v>
+        <v>0.1526642783863188</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1447923902223035</v>
+        <v>0.1224022883286873</v>
       </c>
       <c r="F31" t="n">
-        <v>5.909894706781544</v>
+        <v>5.044753438078005</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>695.2930456525405</v>
+        <v>10.3872973183927</v>
       </c>
       <c r="I31" t="n">
-        <v>3989.464303210069</v>
+        <v>68.04012980762613</v>
       </c>
       <c r="J31" t="n">
-        <v>3.948111421122614</v>
+        <v>0.06012252362922617</v>
       </c>
       <c r="K31" t="n">
-        <v>1.197059399324369</v>
+        <v>1.236353186927701</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.170914493351624</v>
+        <v>0.1450448305974214</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1423253379499558</v>
+        <v>0.1155636178594014</v>
       </c>
       <c r="F32" t="n">
-        <v>5.97829809766438</v>
+        <v>4.919907192636167</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>704.2853859298878</v>
+        <v>10.24150019819266</v>
       </c>
       <c r="I32" t="n">
-        <v>4120.688492350118</v>
+        <v>70.60920514029499</v>
       </c>
       <c r="J32" t="n">
-        <v>3.857194469720434</v>
+        <v>0.05769641311301676</v>
       </c>
       <c r="K32" t="n">
-        <v>1.218468896638028</v>
+        <v>1.241787370485633</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1659421902880723</v>
+        <v>0.1536455263053555</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1381402632976746</v>
+        <v>0.1254337105155339</v>
       </c>
       <c r="F33" t="n">
-        <v>5.968729805865127</v>
+        <v>5.446140987521587</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>704.144342041531</v>
+        <v>11.25208938733311</v>
       </c>
       <c r="I33" t="n">
-        <v>4243.311124308717</v>
+        <v>73.23408404987129</v>
       </c>
       <c r="J33" t="n">
-        <v>3.704027719384901</v>
+        <v>0.06013637117448221</v>
       </c>
       <c r="K33" t="n">
-        <v>1.248331927760494</v>
+        <v>1.265610123660533</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1626770151973614</v>
+        <v>0.1526682416807667</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1354912040024704</v>
+        <v>0.1251574703067656</v>
       </c>
       <c r="F34" t="n">
-        <v>5.98389409943132</v>
+        <v>5.549398801119953</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>703.0416022242489</v>
+        <v>11.53659514727535</v>
       </c>
       <c r="I34" t="n">
-        <v>4321.702124736625</v>
+        <v>75.56643752666432</v>
       </c>
       <c r="J34" t="n">
-        <v>3.578043486341032</v>
+        <v>0.06099893439686253</v>
       </c>
       <c r="K34" t="n">
-        <v>1.245566503017099</v>
+        <v>1.27114312625719</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1694369337011029</v>
+        <v>0.1646273603279859</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1433185982828986</v>
+        <v>0.1383577804640862</v>
       </c>
       <c r="F35" t="n">
-        <v>6.487279184836813</v>
+        <v>6.266844052356549</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>757.6297216340319</v>
+        <v>12.97431101746266</v>
       </c>
       <c r="I35" t="n">
-        <v>4471.455573969113</v>
+        <v>78.8101746369135</v>
       </c>
       <c r="J35" t="n">
-        <v>3.784850847895306</v>
+        <v>0.06828176874620509</v>
       </c>
       <c r="K35" t="n">
-        <v>1.221907526346165</v>
+        <v>1.299002166859342</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1715140802473884</v>
+        <v>0.1716003838956536</v>
       </c>
       <c r="E36" t="n">
-        <v>0.14625536318176</v>
+        <v>0.1463442980388139</v>
       </c>
       <c r="F36" t="n">
-        <v>6.790292626571349</v>
+        <v>6.794417189913889</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>783.6740135721433</v>
+        <v>13.84337415369776</v>
       </c>
       <c r="I36" t="n">
-        <v>4569.152645903986</v>
+        <v>80.67216307695213</v>
       </c>
       <c r="J36" t="n">
-        <v>3.807085593098873</v>
+        <v>0.0714771473070346</v>
       </c>
       <c r="K36" t="n">
-        <v>1.227638716403071</v>
+        <v>1.307048079872188</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1693885902118237</v>
+        <v>0.1843841846097019</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1446680125395566</v>
+        <v>0.1601099043897526</v>
       </c>
       <c r="F37" t="n">
-        <v>6.852129123254785</v>
+        <v>7.595866198255769</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>789.6597658347648</v>
+        <v>15.2867722767284</v>
       </c>
       <c r="I37" t="n">
-        <v>4661.82382678361</v>
+        <v>82.90717725648173</v>
       </c>
       <c r="J37" t="n">
-        <v>3.760511996712128</v>
+        <v>0.07779106863373786</v>
       </c>
       <c r="K37" t="n">
-        <v>1.222345362115942</v>
+        <v>1.306128967696965</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.177518171400859</v>
+        <v>0.1815175166676464</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1537470202852769</v>
+        <v>0.1578619535655552</v>
       </c>
       <c r="F38" t="n">
-        <v>7.467798700101441</v>
+        <v>7.673354292360949</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>849.3642340867139</v>
+        <v>15.49803196151421</v>
       </c>
       <c r="I38" t="n">
-        <v>4784.660789281901</v>
+        <v>85.38036574117905</v>
       </c>
       <c r="J38" t="n">
-        <v>4.007356341706269</v>
+        <v>0.07544979625255926</v>
       </c>
       <c r="K38" t="n">
-        <v>1.243183702408587</v>
+        <v>1.273766146859278</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1830762476806239</v>
+        <v>0.1807708482878866</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1601289512671582</v>
+        <v>0.1577587934645126</v>
       </c>
       <c r="F39" t="n">
-        <v>7.978118397128191</v>
+        <v>7.855484861103005</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>903.0324416441872</v>
+        <v>15.71421626177992</v>
       </c>
       <c r="I39" t="n">
-        <v>4932.548340293305</v>
+        <v>86.92892914212717</v>
       </c>
       <c r="J39" t="n">
-        <v>4.249461513966832</v>
+        <v>0.07483643912971109</v>
       </c>
       <c r="K39" t="n">
-        <v>1.290839791706971</v>
+        <v>1.248316254275815</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1781275569864013</v>
+        <v>0.1864428668851827</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1555486437167971</v>
+        <v>0.1640923961952153</v>
       </c>
       <c r="F40" t="n">
-        <v>7.889111174637263</v>
+        <v>8.341787046519414</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>903.3243832460314</v>
+        <v>16.49398265211139</v>
       </c>
       <c r="I40" t="n">
-        <v>5071.221985686321</v>
+        <v>88.46668648508228</v>
       </c>
       <c r="J40" t="n">
-        <v>4.153582946122683</v>
+        <v>0.07767685784783231</v>
       </c>
       <c r="K40" t="n">
-        <v>1.281167246401544</v>
+        <v>1.254473324319396</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.179661279450708</v>
+        <v>0.1892404488591307</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1577270890616894</v>
+        <v>0.1675623859944015</v>
       </c>
       <c r="F41" t="n">
-        <v>8.190923679620134</v>
+        <v>8.72958299087834</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>929.8807269639433</v>
+        <v>17.14160270783727</v>
       </c>
       <c r="I41" t="n">
-        <v>5175.743653874322</v>
+        <v>90.58107191764991</v>
       </c>
       <c r="J41" t="n">
-        <v>4.149894283544996</v>
+        <v>0.0791033221451057</v>
       </c>
       <c r="K41" t="n">
-        <v>1.259646325029909</v>
+        <v>1.262199954381975</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.179541535699852</v>
+        <v>0.1862987021955897</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1581754298587023</v>
+        <v>0.1651085642319332</v>
       </c>
       <c r="F42" t="n">
-        <v>8.403100547881175</v>
+        <v>8.791764476244234</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>943.4414661298511</v>
+        <v>17.18720544352949</v>
       </c>
       <c r="I42" t="n">
-        <v>5254.725389600355</v>
+        <v>92.25617377347656</v>
       </c>
       <c r="J42" t="n">
-        <v>4.150818474203909</v>
+        <v>0.0776607451233837</v>
       </c>
       <c r="K42" t="n">
-        <v>1.257869605270303</v>
+        <v>1.275738521897643</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.181274772710928</v>
+        <v>0.1869336276292421</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1603889250760027</v>
+        <v>0.1661921385381513</v>
       </c>
       <c r="F43" t="n">
-        <v>8.679311267587737</v>
+        <v>9.012546148846033</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>981.286032853208</v>
+        <v>17.60299955361909</v>
       </c>
       <c r="I43" t="n">
-        <v>5413.25203820847</v>
+        <v>94.16711041703148</v>
       </c>
       <c r="J43" t="n">
-        <v>4.266463213271107</v>
+        <v>0.07732989659063522</v>
       </c>
       <c r="K43" t="n">
-        <v>1.257555442889852</v>
+        <v>1.27366801912998</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1792090753792351</v>
+        <v>0.182900406961222</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1587913906871762</v>
+        <v>0.1625745464378693</v>
       </c>
       <c r="F44" t="n">
-        <v>8.777149715165104</v>
+        <v>8.998409034199806</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>987.7082951914924</v>
+        <v>17.5794798928252</v>
       </c>
       <c r="I44" t="n">
-        <v>5511.485917224581</v>
+        <v>96.1150397907663</v>
       </c>
       <c r="J44" t="n">
-        <v>4.179563987248722</v>
+        <v>0.07515794085784867</v>
       </c>
       <c r="K44" t="n">
-        <v>1.265516940274718</v>
+        <v>1.269889198149219</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1827729557245516</v>
+        <v>0.188882278882885</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1629373478537882</v>
+        <v>0.1691949555547997</v>
       </c>
       <c r="F45" t="n">
-        <v>9.214386416357309</v>
+        <v>9.59410661039084</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1038.66548470414</v>
+        <v>18.59190092237849</v>
       </c>
       <c r="I45" t="n">
-        <v>5682.818229790315</v>
+        <v>98.43115528008981</v>
       </c>
       <c r="J45" t="n">
-        <v>4.28426484800772</v>
+        <v>0.07745866057119964</v>
       </c>
       <c r="K45" t="n">
-        <v>1.265923823045475</v>
+        <v>1.234555982762907</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.186471547502914</v>
+        <v>0.194084991550497</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1671018224434597</v>
+        <v>0.174896538968366</v>
       </c>
       <c r="F46" t="n">
-        <v>9.626958923296471</v>
+        <v>10.1146765597574</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1078.661888003912</v>
+        <v>19.46068212013445</v>
       </c>
       <c r="I46" t="n">
-        <v>5784.59235442906</v>
+        <v>100.2688665654561</v>
       </c>
       <c r="J46" t="n">
-        <v>4.383673373597496</v>
+        <v>0.08006995473826209</v>
       </c>
       <c r="K46" t="n">
-        <v>1.266279069264086</v>
+        <v>1.248919890134363</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1892552850394248</v>
+        <v>0.1919001195697719</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1704007567845277</v>
+        <v>0.1731070990946503</v>
       </c>
       <c r="F47" t="n">
-        <v>10.03765686846445</v>
+        <v>10.21124410649217</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1113.660895912226</v>
+        <v>19.52983072734807</v>
       </c>
       <c r="I47" t="n">
-        <v>5884.437497638352</v>
+        <v>101.7708106234261</v>
       </c>
       <c r="J47" t="n">
-        <v>4.436159608725042</v>
+        <v>0.07883242513113305</v>
       </c>
       <c r="K47" t="n">
-        <v>1.237699336984325</v>
+        <v>1.235752193628493</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1827320963727194</v>
+        <v>0.1874804372215234</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1641578258357358</v>
+        <v>0.1690140835220126</v>
       </c>
       <c r="F48" t="n">
-        <v>9.837915088448694</v>
+        <v>10.1525423086903</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1086.777967975353</v>
+        <v>19.3572124980753</v>
       </c>
       <c r="I48" t="n">
-        <v>5947.384118872291</v>
+        <v>103.2492391470326</v>
       </c>
       <c r="J48" t="n">
-        <v>4.2394196645372</v>
+        <v>0.07556967157149401</v>
       </c>
       <c r="K48" t="n">
-        <v>1.215780049044628</v>
+        <v>1.230596785494211</v>
       </c>
     </row>
     <row r="49">
@@ -2136,28 +2136,28 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1836871092610972</v>
+        <v>0.1894482098569705</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1654658393785324</v>
+        <v>0.1713555359698493</v>
       </c>
       <c r="F49" t="n">
-        <v>10.080916996727</v>
+        <v>10.47099013882212</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1112.638782561442</v>
+        <v>19.8917637361675</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.250217705322</v>
+        <v>104.9984254334489</v>
       </c>
       <c r="J49" t="n">
-        <v>4.265071278523671</v>
+        <v>0.07667485252519253</v>
       </c>
       <c r="K49" t="n">
-        <v>1.21396631625514</v>
+        <v>1.229546439149446</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6579246446791172</v>
+        <v>0.6593915399024814</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3158492893582343</v>
+        <v>0.3187830798049629</v>
       </c>
       <c r="F2" t="n">
-        <v>1.92333248930474</v>
+        <v>1.935922377599465</v>
       </c>
       <c r="G2" t="n">
-        <v>0.044</v>
+        <v>0.025</v>
       </c>
       <c r="H2" t="n">
-        <v>3.114047681002716</v>
+        <v>156.3508735978753</v>
       </c>
       <c r="I2" t="n">
-        <v>4.733137307117441</v>
+        <v>237.113860485681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1606192465262189</v>
+        <v>7.308220321949261</v>
       </c>
       <c r="K2" t="n">
         <v>2.381742084341708</v>
@@ -526,25 +526,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3532165705482233</v>
+        <v>0.349709752392391</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02982485582233496</v>
+        <v>0.02456462858858666</v>
       </c>
       <c r="F3" t="n">
-        <v>1.092225169861308</v>
+        <v>1.075549736995007</v>
       </c>
       <c r="G3" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="H3" t="n">
-        <v>2.642463890044155</v>
+        <v>136.1622267925275</v>
       </c>
       <c r="I3" t="n">
-        <v>7.481143610965981</v>
+        <v>389.3578199093144</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1120830378775509</v>
+        <v>5.459928699510327</v>
       </c>
       <c r="K3" t="n">
         <v>1.557899137099524</v>
@@ -561,25 +561,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2854385399915653</v>
+        <v>0.311298212855479</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03023801855998143</v>
+        <v>0.06533328887529288</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11848729144579</v>
+        <v>1.265620348698808</v>
       </c>
       <c r="G4" t="n">
-        <v>0.335</v>
+        <v>0.204</v>
       </c>
       <c r="H4" t="n">
-        <v>2.788326491281801</v>
+        <v>163.3513678149846</v>
       </c>
       <c r="I4" t="n">
-        <v>9.768570464815983</v>
+        <v>524.7423887101495</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09405825759349087</v>
+        <v>5.703428684009185</v>
       </c>
       <c r="K4" t="n">
         <v>1.534762566826719</v>
@@ -596,25 +596,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3388689749504772</v>
+        <v>0.3588414131055914</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1648871262532344</v>
+        <v>0.1901154691860102</v>
       </c>
       <c r="F5" t="n">
-        <v>1.947726027099327</v>
+        <v>2.126770814076012</v>
       </c>
       <c r="G5" t="n">
-        <v>0.015</v>
+        <v>0.007</v>
       </c>
       <c r="H5" t="n">
-        <v>4.350238375964505</v>
+        <v>243.2779936344178</v>
       </c>
       <c r="I5" t="n">
-        <v>12.83752334246667</v>
+        <v>677.9540620157787</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1435024146267186</v>
+        <v>7.58799404979494</v>
       </c>
       <c r="K5" t="n">
         <v>1.760964712626336</v>
@@ -631,25 +631,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3782934230417848</v>
+        <v>0.3807481116619993</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2487712195088234</v>
+        <v>0.2517373015915825</v>
       </c>
       <c r="F6" t="n">
-        <v>2.920683965552784</v>
+        <v>2.95128843431166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>5.773036539918646</v>
+        <v>316.1805156825353</v>
       </c>
       <c r="I6" t="n">
-        <v>15.26073726975946</v>
+        <v>830.419130123533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1705300806849534</v>
+        <v>8.623541646390784</v>
       </c>
       <c r="K6" t="n">
         <v>1.744503813007251</v>
@@ -666,25 +666,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2835613744606992</v>
+        <v>0.2989941998978144</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1556259056143955</v>
+        <v>0.17381459273671</v>
       </c>
       <c r="F7" t="n">
-        <v>2.216440655729005</v>
+        <v>2.388521634462495</v>
       </c>
       <c r="G7" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>4.835100485385633</v>
+        <v>278.7178253517961</v>
       </c>
       <c r="I7" t="n">
-        <v>17.05133675057625</v>
+        <v>932.1847228041613</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1248407465431917</v>
+        <v>6.386958750861576</v>
       </c>
       <c r="K7" t="n">
         <v>1.849272288296433</v>
@@ -701,25 +701,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2472077078854155</v>
+        <v>0.2590676924845856</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1331482696862359</v>
+        <v>0.1468052216489167</v>
       </c>
       <c r="F8" t="n">
-        <v>2.167358631503358</v>
+        <v>2.307696334813547</v>
       </c>
       <c r="G8" t="n">
-        <v>0.011</v>
+        <v>0.005</v>
       </c>
       <c r="H8" t="n">
-        <v>4.709947937837544</v>
+        <v>271.7940620299304</v>
       </c>
       <c r="I8" t="n">
-        <v>19.05259337633872</v>
+        <v>1049.123722928524</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1033030968368027</v>
+        <v>5.209004302937728</v>
       </c>
       <c r="K8" t="n">
         <v>2.001450672305995</v>
@@ -736,25 +736,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.25094837548363</v>
+        <v>0.2500537808560696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1523889512051603</v>
+        <v>0.151376646758184</v>
       </c>
       <c r="F9" t="n">
-        <v>2.546163163195847</v>
+        <v>2.534060024564775</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>5.236189817651347</v>
+        <v>289.9649830965567</v>
       </c>
       <c r="I9" t="n">
-        <v>20.86560555556542</v>
+        <v>1159.610473010444</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08398596201227704</v>
+        <v>4.404368380121684</v>
       </c>
       <c r="K9" t="n">
         <v>1.525801098174523</v>
@@ -771,25 +771,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2751480018178623</v>
+        <v>0.2659941587589189</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1888560972723696</v>
+        <v>0.1786125109921236</v>
       </c>
       <c r="F10" t="n">
-        <v>3.188572592841613</v>
+        <v>3.044050616541425</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>6.132228811762252</v>
+        <v>329.396294379728</v>
       </c>
       <c r="I10" t="n">
-        <v>22.28701924508817</v>
+        <v>1238.359127571192</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09493454891279297</v>
+        <v>4.835143407981414</v>
       </c>
       <c r="K10" t="n">
         <v>1.50230557236947</v>
@@ -806,25 +806,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.268282848947674</v>
+        <v>0.2831403201183172</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1904405988357245</v>
+        <v>0.2068786520457977</v>
       </c>
       <c r="F11" t="n">
-        <v>3.446494012722404</v>
+        <v>3.71274753456836</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>6.728530441155329</v>
+        <v>407.0080674895702</v>
       </c>
       <c r="I11" t="n">
-        <v>25.07998728784807</v>
+        <v>1437.47830517212</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1014832360555909</v>
+        <v>5.74671287899573</v>
       </c>
       <c r="K11" t="n">
         <v>1.49146893192355</v>
@@ -841,25 +841,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2823756878403189</v>
+        <v>0.2906204103331679</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2133733501326571</v>
+        <v>0.2224108344036648</v>
       </c>
       <c r="F12" t="n">
-        <v>4.092262627922032</v>
+        <v>4.260698096606467</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>7.642427025733995</v>
+        <v>447.2086933582008</v>
       </c>
       <c r="I12" t="n">
-        <v>27.06474868351884</v>
+        <v>1538.806902259616</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1117924196474495</v>
+        <v>5.955239907197557</v>
       </c>
       <c r="K12" t="n">
         <v>1.395266770664399</v>
@@ -876,25 +876,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2858918673242215</v>
+        <v>0.2899897746076708</v>
       </c>
       <c r="E13" t="n">
-        <v>0.222132212621027</v>
+        <v>0.2265960044833557</v>
       </c>
       <c r="F13" t="n">
-        <v>4.483899240908181</v>
+        <v>4.574420704731732</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>8.152648019882438</v>
+        <v>471.5254427547616</v>
       </c>
       <c r="I13" t="n">
-        <v>28.51654402129866</v>
+        <v>1626.007135571217</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1074578215631683</v>
+        <v>5.749795288344258</v>
       </c>
       <c r="K13" t="n">
         <v>1.376403804581479</v>
@@ -911,25 +911,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2703096282531469</v>
+        <v>0.2708756523972145</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2104989420443883</v>
+        <v>0.2111113616101008</v>
       </c>
       <c r="F14" t="n">
-        <v>4.519420280678266</v>
+        <v>4.532399679301824</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>8.715299936248677</v>
+        <v>506.3879787606029</v>
       </c>
       <c r="I14" t="n">
-        <v>32.24191455025323</v>
+        <v>1869.448118644606</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1020266758586354</v>
+        <v>5.530164469587952</v>
       </c>
       <c r="K14" t="n">
         <v>1.340574768793374</v>
@@ -946,25 +946,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.264554337661392</v>
+        <v>0.2635355571267892</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2088387571811944</v>
+        <v>0.2077427963030611</v>
       </c>
       <c r="F15" t="n">
-        <v>4.748300841187857</v>
+        <v>4.723472243279097</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>9.198312212603732</v>
+        <v>528.8311779532429</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7690848462928</v>
+        <v>2006.678657403402</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1043199963201647</v>
+        <v>5.605557014277482</v>
       </c>
       <c r="K15" t="n">
         <v>1.394029296786374</v>
@@ -981,25 +981,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2548527473464362</v>
+        <v>0.2482197812660931</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2016279435854673</v>
+        <v>0.1945211942136712</v>
       </c>
       <c r="F16" t="n">
-        <v>4.788232728691174</v>
+        <v>4.622463921141436</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>9.214223689832377</v>
+        <v>521.5442264212284</v>
       </c>
       <c r="I16" t="n">
-        <v>36.15508871602214</v>
+        <v>2101.138852677216</v>
       </c>
       <c r="J16" t="n">
-        <v>0.09960781211974495</v>
+        <v>5.257002734180564</v>
       </c>
       <c r="K16" t="n">
         <v>1.36021395748662</v>
@@ -1016,25 +1016,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.270570616271733</v>
+        <v>0.2605086092122359</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2219419906898485</v>
+        <v>0.2112091831597184</v>
       </c>
       <c r="F17" t="n">
-        <v>5.564019402854107</v>
+        <v>5.284211806740341</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>10.49480561146374</v>
+        <v>583.790321703515</v>
       </c>
       <c r="I17" t="n">
-        <v>38.78767678499075</v>
+        <v>2240.963642118645</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1059045920777064</v>
+        <v>5.672644961159683</v>
       </c>
       <c r="K17" t="n">
         <v>1.320372237737873</v>
@@ -1051,25 +1051,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2585272602203122</v>
+        <v>0.2526618940653993</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2121852139840816</v>
+        <v>0.2059532624444868</v>
       </c>
       <c r="F18" t="n">
-        <v>5.578675980392816</v>
+        <v>5.409319119344032</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>10.81576955772907</v>
+        <v>616.5769763069443</v>
       </c>
       <c r="I18" t="n">
-        <v>41.83608934899969</v>
+        <v>2440.324365443682</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1035069240624528</v>
+        <v>5.64592619101022</v>
       </c>
       <c r="K18" t="n">
         <v>1.307941320700577</v>
@@ -1086,25 +1086,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2381634173472308</v>
+        <v>0.2403856142252833</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1928160017131375</v>
+        <v>0.1951704722148835</v>
       </c>
       <c r="F19" t="n">
-        <v>5.251973326748378</v>
+        <v>5.316484777820512</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>10.4180269885074</v>
+        <v>603.246060387627</v>
       </c>
       <c r="I19" t="n">
-        <v>43.74318736499491</v>
+        <v>2509.493183823722</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09985274334431969</v>
+        <v>5.419248572071915</v>
       </c>
       <c r="K19" t="n">
         <v>1.285074598382898</v>
@@ -1121,25 +1121,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2370518653525321</v>
+        <v>0.2373984599981324</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1941896105970564</v>
+        <v>0.1945556768519601</v>
       </c>
       <c r="F20" t="n">
-        <v>5.530550520612738</v>
+        <v>5.541154018593257</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>10.9014284561925</v>
+        <v>626.0955835669482</v>
       </c>
       <c r="I20" t="n">
-        <v>45.98752446001815</v>
+        <v>2637.31948207193</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09973109849735637</v>
+        <v>5.428985470805894</v>
       </c>
       <c r="K20" t="n">
         <v>1.29015848663695</v>
@@ -1156,25 +1156,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2214800836835681</v>
+        <v>0.215969214270761</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1800694498369494</v>
+        <v>0.1742654490723973</v>
       </c>
       <c r="F21" t="n">
-        <v>5.348386709170176</v>
+        <v>5.178650254803238</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>10.62592711522805</v>
+        <v>596.0886330695361</v>
       </c>
       <c r="I21" t="n">
-        <v>47.97689678684369</v>
+        <v>2760.062979727373</v>
       </c>
       <c r="J21" t="n">
-        <v>0.09053605556362303</v>
+        <v>4.79401538490333</v>
       </c>
       <c r="K21" t="n">
         <v>1.2364679451503</v>
@@ -1191,25 +1191,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2081966501944755</v>
+        <v>0.2044482099357651</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167798520102357</v>
+        <v>0.1638588328916715</v>
       </c>
       <c r="F22" t="n">
-        <v>5.153620965122173</v>
+        <v>5.036988119173792</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>10.49266200544291</v>
+        <v>587.0671503235816</v>
       </c>
       <c r="I22" t="n">
-        <v>50.39784259565064</v>
+        <v>2871.471217615602</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0886657657222833</v>
+        <v>4.756889607191317</v>
       </c>
       <c r="K22" t="n">
         <v>1.225172581294342</v>
@@ -1226,25 +1226,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.203265281032049</v>
+        <v>0.1993147504573659</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1645888383637019</v>
+        <v>0.1604465344601507</v>
       </c>
       <c r="F23" t="n">
-        <v>5.255531972654808</v>
+        <v>5.127962406909697</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>10.5266299300827</v>
+        <v>588.0241535234984</v>
       </c>
       <c r="I23" t="n">
-        <v>51.78764359872631</v>
+        <v>2950.228982923563</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0842502170661563</v>
+        <v>4.530196743979291</v>
       </c>
       <c r="K23" t="n">
         <v>1.207949575491007</v>
@@ -1261,25 +1261,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1952250522206383</v>
+        <v>0.1903234916546817</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1579669527864085</v>
+        <v>0.1528384681201763</v>
       </c>
       <c r="F24" t="n">
-        <v>5.239801685678079</v>
+        <v>5.077320852672972</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>10.70426964850156</v>
+        <v>596.2055746350318</v>
       </c>
       <c r="I24" t="n">
-        <v>54.83040996400337</v>
+        <v>3132.590566995127</v>
       </c>
       <c r="J24" t="n">
-        <v>0.08164509905794252</v>
+        <v>4.420321166215435</v>
       </c>
       <c r="K24" t="n">
         <v>1.204524834043881</v>
@@ -1296,25 +1296,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1864957273733484</v>
+        <v>0.1871351764156509</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1501785723453728</v>
+        <v>0.1508465682199209</v>
       </c>
       <c r="F25" t="n">
-        <v>5.135196499552032</v>
+        <v>5.156857364335934</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>10.61666405428146</v>
+        <v>608.1351025021513</v>
       </c>
       <c r="I25" t="n">
-        <v>56.92711679677149</v>
+        <v>3249.710258382456</v>
       </c>
       <c r="J25" t="n">
-        <v>0.07757914103192969</v>
+        <v>4.30537906989029</v>
       </c>
       <c r="K25" t="n">
         <v>1.206635847824345</v>
@@ -1331,25 +1331,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1715280714912285</v>
+        <v>0.1761037371491634</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1361232882216228</v>
+        <v>0.1408944951469908</v>
       </c>
       <c r="F26" t="n">
-        <v>4.844771119909164</v>
+        <v>5.001633864719304</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>10.21142681261125</v>
+        <v>591.2522921214282</v>
       </c>
       <c r="I26" t="n">
-        <v>59.53210296038012</v>
+        <v>3357.409114041832</v>
       </c>
       <c r="J26" t="n">
-        <v>0.07136987377933823</v>
+        <v>4.009485757695305</v>
       </c>
       <c r="K26" t="n">
         <v>1.205472488895055</v>
@@ -1366,25 +1366,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1668907619510709</v>
+        <v>0.1726522597060153</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1327469407195575</v>
+        <v>0.1387445654316717</v>
       </c>
       <c r="F27" t="n">
-        <v>4.887875929863316</v>
+        <v>5.091831320322275</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>10.28660837487032</v>
+        <v>598.263906111418</v>
       </c>
       <c r="I27" t="n">
-        <v>61.63677518523258</v>
+        <v>3465.138001264018</v>
       </c>
       <c r="J27" t="n">
-        <v>0.06943400515022734</v>
+        <v>3.915417509676947</v>
       </c>
       <c r="K27" t="n">
         <v>1.205057379429636</v>
@@ -1401,25 +1401,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1649545051665424</v>
+        <v>0.1695782733285889</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1318177791810877</v>
+        <v>0.1366250302067075</v>
       </c>
       <c r="F28" t="n">
-        <v>4.977996475540433</v>
+        <v>5.146026832666635</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>10.40719989779272</v>
+        <v>600.6260719978516</v>
       </c>
       <c r="I28" t="n">
-        <v>63.09133471247323</v>
+        <v>3541.881045303655</v>
       </c>
       <c r="J28" t="n">
-        <v>0.06752476146362883</v>
+        <v>3.802424502270836</v>
       </c>
       <c r="K28" t="n">
         <v>1.201785134710402</v>
@@ -1436,25 +1436,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1575879160011046</v>
+        <v>0.1651171313185214</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1254347830240476</v>
+        <v>0.1332513729719</v>
       </c>
       <c r="F29" t="n">
-        <v>4.901168297147024</v>
+        <v>5.181647633251084</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>10.27880607570618</v>
+        <v>607.8658401834412</v>
       </c>
       <c r="I29" t="n">
-        <v>65.22585193419354</v>
+        <v>3681.422002244149</v>
       </c>
       <c r="J29" t="n">
-        <v>0.06362453768365349</v>
+        <v>3.687747268839953</v>
       </c>
       <c r="K29" t="n">
         <v>1.238134139596283</v>
@@ -1471,25 +1471,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1541419101105417</v>
+        <v>0.1599037889407671</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1230441862175468</v>
+        <v>0.1290178988282952</v>
       </c>
       <c r="F30" t="n">
-        <v>4.956694279006841</v>
+        <v>5.177243989358023</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>10.2839394812705</v>
+        <v>600.1316480216421</v>
       </c>
       <c r="I30" t="n">
-        <v>66.7173481494777</v>
+        <v>3753.07959865759</v>
       </c>
       <c r="J30" t="n">
-        <v>0.06114830129389158</v>
+        <v>3.515367095652828</v>
       </c>
       <c r="K30" t="n">
         <v>1.235652207029463</v>
@@ -1506,25 +1506,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1526642783863188</v>
+        <v>0.1574933774803045</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1224022883286873</v>
+        <v>0.1274038552474582</v>
       </c>
       <c r="F31" t="n">
-        <v>5.044753438078005</v>
+        <v>5.234160125958462</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>10.3872973183927</v>
+        <v>602.858203464128</v>
       </c>
       <c r="I31" t="n">
-        <v>68.04012980762613</v>
+        <v>3827.832084809528</v>
       </c>
       <c r="J31" t="n">
-        <v>0.06012252362922617</v>
+        <v>3.451924533284338</v>
       </c>
       <c r="K31" t="n">
         <v>1.236353186927701</v>
@@ -1541,25 +1541,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1450448305974214</v>
+        <v>0.1521669175806446</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1155636178594014</v>
+        <v>0.1229312940489427</v>
       </c>
       <c r="F32" t="n">
-        <v>4.919907192636167</v>
+        <v>5.204845978935288</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>10.24150019819266</v>
+        <v>602.0442693649585</v>
       </c>
       <c r="I32" t="n">
-        <v>70.60920514029499</v>
+        <v>3956.472792753328</v>
       </c>
       <c r="J32" t="n">
-        <v>0.05769641311301676</v>
+        <v>3.329590433227407</v>
       </c>
       <c r="K32" t="n">
         <v>1.241787370485633</v>
@@ -1576,25 +1576,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1536455263053555</v>
+        <v>0.1633756028956473</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1254337105155339</v>
+        <v>0.1354881229921688</v>
       </c>
       <c r="F33" t="n">
-        <v>5.446140987521587</v>
+        <v>5.858385320620866</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>11.25208938733311</v>
+        <v>673.5723513119648</v>
       </c>
       <c r="I33" t="n">
-        <v>73.23408404987129</v>
+        <v>4122.845390460133</v>
       </c>
       <c r="J33" t="n">
-        <v>0.06013637117448221</v>
+        <v>3.610798928486568</v>
       </c>
       <c r="K33" t="n">
         <v>1.265610123660533</v>
@@ -1611,25 +1611,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1526682416807667</v>
+        <v>0.1599338330378758</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1251574703067656</v>
+        <v>0.1326589574871574</v>
       </c>
       <c r="F34" t="n">
-        <v>5.549398801119953</v>
+        <v>5.863778653745819</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>11.53659514727535</v>
+        <v>683.5471447917865</v>
       </c>
       <c r="I34" t="n">
-        <v>75.56643752666432</v>
+        <v>4273.937113918277</v>
       </c>
       <c r="J34" t="n">
-        <v>0.06099893439686253</v>
+        <v>3.611482849027618</v>
       </c>
       <c r="K34" t="n">
         <v>1.27114312625719</v>
@@ -1646,25 +1646,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1646273603279859</v>
+        <v>0.1706430925637629</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1383577804640862</v>
+        <v>0.1445626866695416</v>
       </c>
       <c r="F35" t="n">
-        <v>6.266844052356549</v>
+        <v>6.542961534259433</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>12.97431101746266</v>
+        <v>758.455523620292</v>
       </c>
       <c r="I35" t="n">
-        <v>78.8101746369135</v>
+        <v>4444.689276460959</v>
       </c>
       <c r="J35" t="n">
-        <v>0.06828176874620509</v>
+        <v>3.979701590754225</v>
       </c>
       <c r="K35" t="n">
         <v>1.299002166859342</v>
@@ -1681,25 +1681,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1716003838956536</v>
+        <v>0.1751903528754152</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1463442980388139</v>
+        <v>0.1500437172923487</v>
       </c>
       <c r="F36" t="n">
-        <v>6.794417189913889</v>
+        <v>6.966751170219601</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>13.84337415369776</v>
+        <v>800.6819184054136</v>
       </c>
       <c r="I36" t="n">
-        <v>80.67216307695213</v>
+        <v>4570.35393367128</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0714771473070346</v>
+        <v>4.101329719933307</v>
       </c>
       <c r="K36" t="n">
         <v>1.307048079872188</v>
@@ -1716,25 +1716,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1843841846097019</v>
+        <v>0.1863756866969237</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1601099043897526</v>
+        <v>0.1621606773724275</v>
       </c>
       <c r="F37" t="n">
-        <v>7.595866198255769</v>
+        <v>7.696701008840122</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>15.2867722767284</v>
+        <v>880.9781682547286</v>
       </c>
       <c r="I37" t="n">
-        <v>82.90717725648173</v>
+        <v>4726.894284700011</v>
       </c>
       <c r="J37" t="n">
-        <v>0.07779106863373786</v>
+        <v>4.467172730604004</v>
       </c>
       <c r="K37" t="n">
         <v>1.306128967696965</v>
@@ -1751,25 +1751,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1815175166676464</v>
+        <v>0.1817299536282213</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1578619535655552</v>
+        <v>0.1580805303226785</v>
       </c>
       <c r="F38" t="n">
-        <v>7.673354292360949</v>
+        <v>7.684329181322112</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>15.49803196151421</v>
+        <v>888.1125665934284</v>
       </c>
       <c r="I38" t="n">
-        <v>85.38036574117905</v>
+        <v>4886.990553083545</v>
       </c>
       <c r="J38" t="n">
-        <v>0.07544979625255926</v>
+        <v>4.290802557546684</v>
       </c>
       <c r="K38" t="n">
         <v>1.273766146859278</v>
@@ -1786,25 +1786,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1807708482878866</v>
+        <v>0.1813679770515466</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1577587934645126</v>
+        <v>0.1583726955080508</v>
       </c>
       <c r="F39" t="n">
-        <v>7.855484861103005</v>
+        <v>7.887182277307045</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>15.71421626177992</v>
+        <v>908.2037946758132</v>
       </c>
       <c r="I39" t="n">
-        <v>86.92892914212717</v>
+        <v>5007.520122572094</v>
       </c>
       <c r="J39" t="n">
-        <v>0.07483643912971109</v>
+        <v>4.276516950443937</v>
       </c>
       <c r="K39" t="n">
         <v>1.248316254275815</v>
@@ -1821,25 +1821,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1864428668851827</v>
+        <v>0.188082169054524</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1640923961952153</v>
+        <v>0.1657767341384396</v>
       </c>
       <c r="F40" t="n">
-        <v>8.341787046519414</v>
+        <v>8.432122922602041</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>16.49398265211139</v>
+        <v>961.8776095737393</v>
       </c>
       <c r="I40" t="n">
-        <v>88.46668648508228</v>
+        <v>5114.135031561104</v>
       </c>
       <c r="J40" t="n">
-        <v>0.07767685784783231</v>
+        <v>4.464449536444511</v>
       </c>
       <c r="K40" t="n">
         <v>1.254473324319396</v>
@@ -1856,25 +1856,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1892404488591307</v>
+        <v>0.1875804634848242</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1675623859944015</v>
+        <v>0.1658580159844184</v>
       </c>
       <c r="F41" t="n">
-        <v>8.72958299087834</v>
+        <v>8.635328200531742</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>17.14160270783727</v>
+        <v>989.5230915970737</v>
       </c>
       <c r="I41" t="n">
-        <v>90.58107191764991</v>
+        <v>5275.192699783092</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0791033221451057</v>
+        <v>4.449181061574883</v>
       </c>
       <c r="K41" t="n">
         <v>1.262199954381975</v>
@@ -1891,25 +1891,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1862987021955897</v>
+        <v>0.1849168268801351</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1651085642319332</v>
+        <v>0.1636907025801385</v>
       </c>
       <c r="F42" t="n">
-        <v>8.791764476244234</v>
+        <v>8.711756525432472</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>17.18720544352949</v>
+        <v>993.5090219948088</v>
       </c>
       <c r="I42" t="n">
-        <v>92.25617377347656</v>
+        <v>5372.734535612657</v>
       </c>
       <c r="J42" t="n">
-        <v>0.0776607451233837</v>
+        <v>4.375313741341381</v>
       </c>
       <c r="K42" t="n">
         <v>1.275738521897643</v>
@@ -1926,25 +1926,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1869336276292421</v>
+        <v>0.1890949823707049</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1661921385381513</v>
+        <v>0.1684086298801617</v>
       </c>
       <c r="F43" t="n">
-        <v>9.012546148846033</v>
+        <v>9.141049996955699</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>17.60299955361909</v>
+        <v>1034.696433565156</v>
       </c>
       <c r="I43" t="n">
-        <v>94.16711041703148</v>
+        <v>5471.834422008724</v>
       </c>
       <c r="J43" t="n">
-        <v>0.07732989659063522</v>
+        <v>4.458642330012155</v>
       </c>
       <c r="K43" t="n">
         <v>1.27366801912998</v>
@@ -1961,25 +1961,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.182900406961222</v>
+        <v>0.1863582871953975</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1625745464378693</v>
+        <v>0.166118443593293</v>
       </c>
       <c r="F44" t="n">
-        <v>8.998409034199806</v>
+        <v>9.207496404568067</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>17.5794798928252</v>
+        <v>1041.125847101225</v>
       </c>
       <c r="I44" t="n">
-        <v>96.1150397907663</v>
+        <v>5586.689289591935</v>
       </c>
       <c r="J44" t="n">
-        <v>0.07515794085784867</v>
+        <v>4.370042373374043</v>
       </c>
       <c r="K44" t="n">
         <v>1.269889198149219</v>
@@ -1996,25 +1996,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.188882278882885</v>
+        <v>0.190632854535389</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1691949555547997</v>
+        <v>0.1709880209076072</v>
       </c>
       <c r="F45" t="n">
-        <v>9.59410661039084</v>
+        <v>9.703968898255017</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>18.59190092237849</v>
+        <v>1080.741557105266</v>
       </c>
       <c r="I45" t="n">
-        <v>98.43115528008981</v>
+        <v>5669.230310479549</v>
       </c>
       <c r="J45" t="n">
-        <v>0.07745866057119964</v>
+        <v>4.43266451165555</v>
       </c>
       <c r="K45" t="n">
         <v>1.234555982762907</v>
@@ -2031,25 +2031,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.194084991550497</v>
+        <v>0.1955521013250359</v>
       </c>
       <c r="E46" t="n">
-        <v>0.174896538968366</v>
+        <v>0.176398579928013</v>
       </c>
       <c r="F46" t="n">
-        <v>10.1146765597574</v>
+        <v>10.20972056634091</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>19.46068212013445</v>
+        <v>1127.879482466792</v>
       </c>
       <c r="I46" t="n">
-        <v>100.2688665654561</v>
+        <v>5767.667413566132</v>
       </c>
       <c r="J46" t="n">
-        <v>0.08006995473826209</v>
+        <v>4.58377454179599</v>
       </c>
       <c r="K46" t="n">
         <v>1.248919890134363</v>
@@ -2066,25 +2066,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1919001195697719</v>
+        <v>0.1914631234144956</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1731070990946503</v>
+        <v>0.1726599402380884</v>
       </c>
       <c r="F47" t="n">
-        <v>10.21124410649217</v>
+        <v>10.1824846154097</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>19.52983072734807</v>
+        <v>1123.004033105776</v>
       </c>
       <c r="I47" t="n">
-        <v>101.7708106234261</v>
+        <v>5865.380304459997</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07883242513113305</v>
+        <v>4.480474852717253</v>
       </c>
       <c r="K47" t="n">
         <v>1.235752193628493</v>
@@ -2101,25 +2101,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1874804372215234</v>
+        <v>0.1897500027415846</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1690140835220126</v>
+        <v>0.1713352300766207</v>
       </c>
       <c r="F48" t="n">
-        <v>10.1525423086903</v>
+        <v>10.3042272741495</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>19.3572124980753</v>
+        <v>1128.652080506234</v>
       </c>
       <c r="I48" t="n">
-        <v>103.2492391470326</v>
+        <v>5948.100470087027</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07556967157149401</v>
+        <v>4.398304647439809</v>
       </c>
       <c r="K48" t="n">
         <v>1.230596785494211</v>
@@ -2136,25 +2136,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1894482098569705</v>
+        <v>0.1907518279659292</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1713555359698493</v>
+        <v>0.1726882526973115</v>
       </c>
       <c r="F49" t="n">
-        <v>10.47099013882212</v>
+        <v>10.56002619245192</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>19.8917637361675</v>
+        <v>1155.571468517169</v>
       </c>
       <c r="I49" t="n">
-        <v>104.9984254334489</v>
+        <v>6057.983720730425</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07667485252519253</v>
+        <v>4.4281495345876</v>
       </c>
       <c r="K49" t="n">
         <v>1.229546439149446</v>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -488,31 +488,31 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6593915399024814</v>
+        <v>0.5147587017934384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3187830798049629</v>
+        <v>0.245180202789793</v>
       </c>
       <c r="F2" t="n">
-        <v>1.935922377599465</v>
+        <v>1.909494650708317</v>
       </c>
       <c r="G2" t="n">
-        <v>0.025</v>
+        <v>0.061</v>
       </c>
       <c r="H2" t="n">
-        <v>156.3508735978753</v>
+        <v>160.1181177351012</v>
       </c>
       <c r="I2" t="n">
-        <v>237.113860485681</v>
+        <v>311.0547081132261</v>
       </c>
       <c r="J2" t="n">
-        <v>7.308220321949261</v>
+        <v>8.956190969726547</v>
       </c>
       <c r="K2" t="n">
-        <v>2.381742084341708</v>
+        <v>3.481990327321756</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +523,31 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.349709752392391</v>
+        <v>0.4618881023525475</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02456462858858666</v>
+        <v>0.2825174698033968</v>
       </c>
       <c r="F3" t="n">
-        <v>1.075549736995007</v>
+        <v>2.57504863415131</v>
       </c>
       <c r="G3" t="n">
-        <v>0.385</v>
+        <v>0.003</v>
       </c>
       <c r="H3" t="n">
-        <v>136.1622267925275</v>
+        <v>194.3602890317141</v>
       </c>
       <c r="I3" t="n">
-        <v>389.3578199093144</v>
+        <v>420.7951840321789</v>
       </c>
       <c r="J3" t="n">
-        <v>5.459928699510327</v>
+        <v>7.171770335410962</v>
       </c>
       <c r="K3" t="n">
-        <v>1.557899137099524</v>
+        <v>2.117605628966524</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.311298212855479</v>
+        <v>0.3385921314884081</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06533328887529288</v>
+        <v>0.1811140675570766</v>
       </c>
       <c r="F4" t="n">
-        <v>1.265620348698808</v>
+        <v>2.150090768426338</v>
       </c>
       <c r="G4" t="n">
-        <v>0.204</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
-        <v>163.3513678149846</v>
+        <v>196.7483119398033</v>
       </c>
       <c r="I4" t="n">
-        <v>524.7423887101495</v>
+        <v>581.0776259770794</v>
       </c>
       <c r="J4" t="n">
-        <v>5.703428684009185</v>
+        <v>5.107108175526919</v>
       </c>
       <c r="K4" t="n">
-        <v>1.534762566826719</v>
+        <v>2.122914290111254</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +593,31 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3588414131055914</v>
+        <v>0.3187459248023032</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1901154691860102</v>
+        <v>0.197093411374143</v>
       </c>
       <c r="F5" t="n">
-        <v>2.126770814076012</v>
+        <v>2.620134313875342</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>243.2779936344178</v>
+        <v>223.8963206603861</v>
       </c>
       <c r="I5" t="n">
-        <v>677.9540620157787</v>
+        <v>702.4288100287212</v>
       </c>
       <c r="J5" t="n">
-        <v>7.58799404979494</v>
+        <v>4.128371768596845</v>
       </c>
       <c r="K5" t="n">
-        <v>1.760964712626336</v>
+        <v>1.966191696689044</v>
       </c>
     </row>
     <row r="6">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3807481116619993</v>
+        <v>0.2430221622433429</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2517373015915825</v>
+        <v>0.1317018919850109</v>
       </c>
       <c r="F6" t="n">
-        <v>2.95128843431166</v>
+        <v>2.183089941116573</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H6" t="n">
-        <v>316.1805156825353</v>
+        <v>192.1938514716771</v>
       </c>
       <c r="I6" t="n">
-        <v>830.419130123533</v>
+        <v>790.8490719427871</v>
       </c>
       <c r="J6" t="n">
-        <v>8.623541646390784</v>
+        <v>3.255084905864639</v>
       </c>
       <c r="K6" t="n">
-        <v>1.744503813007251</v>
+        <v>1.773737763539221</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2989941998978144</v>
+        <v>0.2077666457632025</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17381459273671</v>
+        <v>0.1087374764836028</v>
       </c>
       <c r="F7" t="n">
-        <v>2.388521634462495</v>
+        <v>2.09803482423035</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002</v>
+        <v>0.006</v>
       </c>
       <c r="H7" t="n">
-        <v>278.7178253517961</v>
+        <v>194.7357432010168</v>
       </c>
       <c r="I7" t="n">
-        <v>932.1847228041613</v>
+        <v>937.2810659077712</v>
       </c>
       <c r="J7" t="n">
-        <v>6.386958750861576</v>
+        <v>2.908637671542315</v>
       </c>
       <c r="K7" t="n">
-        <v>1.849272288296433</v>
+        <v>1.486970907301779</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2590676924845856</v>
+        <v>0.1923887742986801</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1468052216489167</v>
+        <v>0.1046049454181018</v>
       </c>
       <c r="F8" t="n">
-        <v>2.307696334813547</v>
+        <v>2.191619763594582</v>
       </c>
       <c r="G8" t="n">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>271.7940620299304</v>
+        <v>223.0659753246838</v>
       </c>
       <c r="I8" t="n">
-        <v>1049.123722928524</v>
+        <v>1159.454215235957</v>
       </c>
       <c r="J8" t="n">
-        <v>5.209004302937728</v>
+        <v>3.150722392126704</v>
       </c>
       <c r="K8" t="n">
-        <v>2.001450672305995</v>
+        <v>1.463228472907605</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2500537808560696</v>
+        <v>0.1896100590229962</v>
       </c>
       <c r="E9" t="n">
-        <v>0.151376646758184</v>
+        <v>0.1116879493136688</v>
       </c>
       <c r="F9" t="n">
-        <v>2.534060024564775</v>
+        <v>2.433328098152094</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>289.9649830965567</v>
+        <v>246.7926940076895</v>
       </c>
       <c r="I9" t="n">
-        <v>1159.610473010444</v>
+        <v>1301.580176069447</v>
       </c>
       <c r="J9" t="n">
-        <v>4.404368380121684</v>
+        <v>3.24620038613105</v>
       </c>
       <c r="K9" t="n">
-        <v>1.525801098174523</v>
+        <v>1.575881546700178</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2659941587589189</v>
+        <v>0.1973484266402454</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1786125109921236</v>
+        <v>0.1293271068639951</v>
       </c>
       <c r="F10" t="n">
-        <v>3.044050616541425</v>
+        <v>2.901273119801324</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>329.396294379728</v>
+        <v>302.1893618734298</v>
       </c>
       <c r="I10" t="n">
-        <v>1238.359127571192</v>
+        <v>1531.247889927713</v>
       </c>
       <c r="J10" t="n">
-        <v>4.835143407981414</v>
+        <v>3.351606621551049</v>
       </c>
       <c r="K10" t="n">
-        <v>1.50230557236947</v>
+        <v>1.635293375666821</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2831403201183172</v>
+        <v>0.1817869856104005</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2068786520457977</v>
+        <v>0.1188475229650467</v>
       </c>
       <c r="F11" t="n">
-        <v>3.71274753456836</v>
+        <v>2.888283089334891</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>407.0080674895702</v>
+        <v>297.5538942650571</v>
       </c>
       <c r="I11" t="n">
-        <v>1437.47830517212</v>
+        <v>1636.827263876657</v>
       </c>
       <c r="J11" t="n">
-        <v>5.74671287899573</v>
+        <v>3.106340858580024</v>
       </c>
       <c r="K11" t="n">
-        <v>1.49146893192355</v>
+        <v>1.587370365693271</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2906204103331679</v>
+        <v>0.1768647984297352</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2224108344036648</v>
+        <v>0.1188975307135195</v>
       </c>
       <c r="F12" t="n">
-        <v>4.260698096606467</v>
+        <v>3.051114972256297</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>447.2086933582008</v>
+        <v>314.1445056850122</v>
       </c>
       <c r="I12" t="n">
-        <v>1538.806902259616</v>
+        <v>1776.184455437668</v>
       </c>
       <c r="J12" t="n">
-        <v>5.955239907197557</v>
+        <v>3.067690139229773</v>
       </c>
       <c r="K12" t="n">
-        <v>1.395266770664399</v>
+        <v>1.555455120678307</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2899897746076708</v>
+        <v>0.16896822992055</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2265960044833557</v>
+        <v>0.115005127967339</v>
       </c>
       <c r="F13" t="n">
-        <v>4.574420704731732</v>
+        <v>3.131180821796618</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>471.5254427547616</v>
+        <v>331.9638178719993</v>
       </c>
       <c r="I13" t="n">
-        <v>1626.007135571217</v>
+        <v>1964.652278289776</v>
       </c>
       <c r="J13" t="n">
-        <v>5.749795288344258</v>
+        <v>2.919451804538109</v>
       </c>
       <c r="K13" t="n">
-        <v>1.376403804581479</v>
+        <v>1.565447140152733</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2708756523972145</v>
+        <v>0.1544863276619849</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2111113616101008</v>
+        <v>0.1035517690874056</v>
       </c>
       <c r="F14" t="n">
-        <v>4.532399679301824</v>
+        <v>3.03303556534771</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>506.3879787606029</v>
+        <v>329.5219445844546</v>
       </c>
       <c r="I14" t="n">
-        <v>1869.448118644606</v>
+        <v>2133.016879690781</v>
       </c>
       <c r="J14" t="n">
-        <v>5.530164469587952</v>
+        <v>2.735826454424792</v>
       </c>
       <c r="K14" t="n">
-        <v>1.340574768793374</v>
+        <v>1.508829584936505</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2635355571267892</v>
+        <v>0.145246836784274</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2077427963030611</v>
+        <v>0.09776054993895589</v>
       </c>
       <c r="F15" t="n">
-        <v>4.723472243279097</v>
+        <v>3.058711186608488</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>528.8311779532429</v>
+        <v>330.3110299114203</v>
       </c>
       <c r="I15" t="n">
-        <v>2006.678657403402</v>
+        <v>2274.135789972559</v>
       </c>
       <c r="J15" t="n">
-        <v>5.605557014277482</v>
+        <v>2.585180407528967</v>
       </c>
       <c r="K15" t="n">
-        <v>1.394029296786374</v>
+        <v>1.531332718794198</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2482197812660931</v>
+        <v>0.1417379508062178</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1945211942136712</v>
+        <v>0.09703680241070844</v>
       </c>
       <c r="F16" t="n">
-        <v>4.622463921141436</v>
+        <v>3.170789921371602</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>521.5442264212284</v>
+        <v>346.1892613529878</v>
       </c>
       <c r="I16" t="n">
-        <v>2101.138852677216</v>
+        <v>2442.459901415486</v>
       </c>
       <c r="J16" t="n">
-        <v>5.257002734180564</v>
+        <v>2.499569380849095</v>
       </c>
       <c r="K16" t="n">
-        <v>1.36021395748662</v>
+        <v>1.472524822221151</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2605086092122359</v>
+        <v>0.1405666541727946</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2112091831597184</v>
+        <v>0.09843756859302955</v>
       </c>
       <c r="F17" t="n">
-        <v>5.284211806740341</v>
+        <v>3.336570263473989</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>583.790321703515</v>
+        <v>356.6716124784796</v>
       </c>
       <c r="I17" t="n">
-        <v>2240.963642118645</v>
+        <v>2537.384236520515</v>
       </c>
       <c r="J17" t="n">
-        <v>5.672644961159683</v>
+        <v>2.41724553427446</v>
       </c>
       <c r="K17" t="n">
-        <v>1.320372237737873</v>
+        <v>1.459079278275009</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2526618940653993</v>
+        <v>0.1519055595032549</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2059532624444868</v>
+        <v>0.1126419279987759</v>
       </c>
       <c r="F18" t="n">
-        <v>5.409319119344032</v>
+        <v>3.868861684022439</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>616.5769763069443</v>
+        <v>437.6406726015339</v>
       </c>
       <c r="I18" t="n">
-        <v>2440.324365443682</v>
+        <v>2881.004974621463</v>
       </c>
       <c r="J18" t="n">
-        <v>5.64592619101022</v>
+        <v>2.980866887398515</v>
       </c>
       <c r="K18" t="n">
-        <v>1.307941320700577</v>
+        <v>1.371381242818427</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2403856142252833</v>
+        <v>0.1605233277105302</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1951704722148835</v>
+        <v>0.1237041754171325</v>
       </c>
       <c r="F19" t="n">
-        <v>5.316484777820512</v>
+        <v>4.359777933815017</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>603.246060387627</v>
+        <v>494.1821347291203</v>
       </c>
       <c r="I19" t="n">
-        <v>2509.493183823722</v>
+        <v>3078.568964258409</v>
       </c>
       <c r="J19" t="n">
-        <v>5.419248572071915</v>
+        <v>3.3399913588364</v>
       </c>
       <c r="K19" t="n">
-        <v>1.285074598382898</v>
+        <v>1.394160381148344</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2373984599981324</v>
+        <v>0.1482539135397079</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1945556768519601</v>
+        <v>0.1130577942644891</v>
       </c>
       <c r="F20" t="n">
-        <v>5.541154018593257</v>
+        <v>4.212223295995375</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>626.0955835669482</v>
+        <v>482.3148646215104</v>
       </c>
       <c r="I20" t="n">
-        <v>2637.31948207193</v>
+        <v>3253.302750030464</v>
       </c>
       <c r="J20" t="n">
-        <v>5.428985470805894</v>
+        <v>3.058564197126362</v>
       </c>
       <c r="K20" t="n">
-        <v>1.29015848663695</v>
+        <v>1.361188245001207</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.215969214270761</v>
+        <v>0.1606482326385549</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1742654490723973</v>
+        <v>0.1276028874668446</v>
       </c>
       <c r="F21" t="n">
-        <v>5.178650254803238</v>
+        <v>4.86144816475039</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>596.0886330695361</v>
+        <v>555.9845322559945</v>
       </c>
       <c r="I21" t="n">
-        <v>2760.062979727373</v>
+        <v>3460.881723528905</v>
       </c>
       <c r="J21" t="n">
-        <v>4.79401538490333</v>
+        <v>3.439784126996339</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2364679451503</v>
+        <v>1.382496111856729</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2044482099357651</v>
+        <v>0.1534813844956585</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1638588328916715</v>
+        <v>0.1216573763939915</v>
       </c>
       <c r="F22" t="n">
-        <v>5.036988119173792</v>
+        <v>4.82281754093756</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>587.0671503235816</v>
+        <v>553.7864986034008</v>
       </c>
       <c r="I22" t="n">
-        <v>2871.471217615602</v>
+        <v>3608.167208180648</v>
       </c>
       <c r="J22" t="n">
-        <v>4.756889607191317</v>
+        <v>3.236328151649229</v>
       </c>
       <c r="K22" t="n">
-        <v>1.225172581294342</v>
+        <v>1.318518790179633</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1993147504573659</v>
+        <v>0.1591167856497036</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1604465344601507</v>
+        <v>0.1288691880112037</v>
       </c>
       <c r="F23" t="n">
-        <v>5.127962406909697</v>
+        <v>5.260476800550133</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>588.0241535234984</v>
+        <v>606.8796161236658</v>
       </c>
       <c r="I23" t="n">
-        <v>2950.228982923563</v>
+        <v>3814.051507172313</v>
       </c>
       <c r="J23" t="n">
-        <v>4.530196743979291</v>
+        <v>3.393096436247743</v>
       </c>
       <c r="K23" t="n">
-        <v>1.207949575491007</v>
+        <v>1.273872516749853</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1903234916546817</v>
+        <v>0.1575361066806408</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1528384681201763</v>
+        <v>0.128485627600663</v>
       </c>
       <c r="F24" t="n">
-        <v>5.077320852672972</v>
+        <v>5.422840230859307</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>596.2055746350318</v>
+        <v>621.6884810086856</v>
       </c>
       <c r="I24" t="n">
-        <v>3132.590566995127</v>
+        <v>3946.323760996457</v>
       </c>
       <c r="J24" t="n">
-        <v>4.420321166215435</v>
+        <v>3.320052789301816</v>
       </c>
       <c r="K24" t="n">
-        <v>1.204524834043881</v>
+        <v>1.252246579166379</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1293,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1871351764156509</v>
+        <v>0.1605410242692418</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1508465682199209</v>
+        <v>0.1329272421728352</v>
       </c>
       <c r="F25" t="n">
-        <v>5.156857364335934</v>
+        <v>5.813800648848229</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>608.1351025021513</v>
+        <v>665.3668770238741</v>
       </c>
       <c r="I25" t="n">
-        <v>3249.710258382456</v>
+        <v>4144.528665196465</v>
       </c>
       <c r="J25" t="n">
-        <v>4.30537906989029</v>
+        <v>3.426476175230086</v>
       </c>
       <c r="K25" t="n">
-        <v>1.206635847824345</v>
+        <v>1.255878983410537</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1328,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1761037371491634</v>
+        <v>0.156177827060109</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1408944951469908</v>
+        <v>0.1294745937392265</v>
       </c>
       <c r="F26" t="n">
-        <v>5.001633864719304</v>
+        <v>5.84864855814947</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>591.2522921214282</v>
+        <v>678.3657769014803</v>
       </c>
       <c r="I26" t="n">
-        <v>3357.409114041832</v>
+        <v>4343.547286263587</v>
       </c>
       <c r="J26" t="n">
-        <v>4.009485757695305</v>
+        <v>3.314020972045142</v>
       </c>
       <c r="K26" t="n">
-        <v>1.205472488895055</v>
+        <v>1.23478078380374</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1363,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1726522597060153</v>
+        <v>0.1415131641727738</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1387445654316717</v>
+        <v>0.1153397850316998</v>
       </c>
       <c r="F27" t="n">
-        <v>5.091831320322275</v>
+        <v>5.406759418033902</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>598.263906111418</v>
+        <v>633.3594098475772</v>
       </c>
       <c r="I27" t="n">
-        <v>3465.138001264018</v>
+        <v>4475.621851507095</v>
       </c>
       <c r="J27" t="n">
-        <v>3.915417509676947</v>
+        <v>2.949133506500223</v>
       </c>
       <c r="K27" t="n">
-        <v>1.205057379429636</v>
+        <v>1.214409525824159</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1398,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1695782733285889</v>
+        <v>0.1432101660244682</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1366250302067075</v>
+        <v>0.118010465025188</v>
       </c>
       <c r="F28" t="n">
-        <v>5.146026832666635</v>
+        <v>5.683010525742271</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>600.6260719978516</v>
+        <v>659.618290419342</v>
       </c>
       <c r="I28" t="n">
-        <v>3541.881045303655</v>
+        <v>4605.945993433474</v>
       </c>
       <c r="J28" t="n">
-        <v>3.802424502270836</v>
+        <v>2.943601020497089</v>
       </c>
       <c r="K28" t="n">
-        <v>1.201785134710402</v>
+        <v>1.218890923111386</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1433,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1651171313185214</v>
+        <v>0.1325927243137736</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1332513729719</v>
+        <v>0.1079504721635969</v>
       </c>
       <c r="F29" t="n">
-        <v>5.181647633251084</v>
+        <v>5.380706418622615</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>607.8658401834412</v>
+        <v>627.1490940114377</v>
       </c>
       <c r="I29" t="n">
-        <v>3681.422002244149</v>
+        <v>4729.890702956843</v>
       </c>
       <c r="J29" t="n">
-        <v>3.687747268839953</v>
+        <v>2.711216381665019</v>
       </c>
       <c r="K29" t="n">
-        <v>1.238134139596283</v>
+        <v>1.181035782567216</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1468,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1599037889407671</v>
+        <v>0.1356336330042883</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1290178988282952</v>
+        <v>0.1120170656000339</v>
       </c>
       <c r="F30" t="n">
-        <v>5.177243989358023</v>
+        <v>5.74315609388071</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>600.1316480216421</v>
+        <v>667.4450314428525</v>
       </c>
       <c r="I30" t="n">
-        <v>3753.07959865759</v>
+        <v>4920.940453034609</v>
       </c>
       <c r="J30" t="n">
-        <v>3.515367095652828</v>
+        <v>2.795186401438425</v>
       </c>
       <c r="K30" t="n">
-        <v>1.235652207029463</v>
+        <v>1.17054023221836</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1503,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1574933774803045</v>
+        <v>0.1540806599036129</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1274038552474582</v>
+        <v>0.1317018413825444</v>
       </c>
       <c r="F31" t="n">
-        <v>5.234160125958462</v>
+        <v>6.885111461918972</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>602.858203464128</v>
+        <v>797.2703050217228</v>
       </c>
       <c r="I31" t="n">
-        <v>3827.832084809528</v>
+        <v>5174.369745823165</v>
       </c>
       <c r="J31" t="n">
-        <v>3.451924533284338</v>
+        <v>3.367422351129779</v>
       </c>
       <c r="K31" t="n">
-        <v>1.236353186927701</v>
+        <v>1.222576898122977</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1538,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1521669175806446</v>
+        <v>0.1539836050417257</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1229312940489427</v>
+        <v>0.1322908769658726</v>
       </c>
       <c r="F32" t="n">
-        <v>5.204845978935288</v>
+        <v>7.098397421628557</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>602.0442693649585</v>
+        <v>822.1683471147162</v>
       </c>
       <c r="I32" t="n">
-        <v>3956.472792753328</v>
+        <v>5339.3239292711</v>
       </c>
       <c r="J32" t="n">
-        <v>3.329590433227407</v>
+        <v>3.426675183845178</v>
       </c>
       <c r="K32" t="n">
-        <v>1.241787370485633</v>
+        <v>1.188548367318493</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1573,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1633756028956473</v>
+        <v>0.1552958135032351</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1354881229921688</v>
+        <v>0.1342832715505793</v>
       </c>
       <c r="F33" t="n">
-        <v>5.858385320620866</v>
+        <v>7.390624792237798</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>673.5723513119648</v>
+        <v>842.1866452319721</v>
       </c>
       <c r="I33" t="n">
-        <v>4122.845390460133</v>
+        <v>5423.112357207412</v>
       </c>
       <c r="J33" t="n">
-        <v>3.610798928486568</v>
+        <v>3.392038663387215</v>
       </c>
       <c r="K33" t="n">
-        <v>1.265610123660533</v>
+        <v>1.17927797941213</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1608,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1599338330378758</v>
+        <v>0.165689134729284</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1326589574871574</v>
+        <v>0.1455366983700878</v>
       </c>
       <c r="F34" t="n">
-        <v>5.863778653745819</v>
+        <v>8.22179173654485</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>683.5471447917865</v>
+        <v>938.7177282839104</v>
       </c>
       <c r="I34" t="n">
-        <v>4273.937113918277</v>
+        <v>5665.535822959435</v>
       </c>
       <c r="J34" t="n">
-        <v>3.611482849027618</v>
+        <v>3.742755387772072</v>
       </c>
       <c r="K34" t="n">
-        <v>1.27114312625719</v>
+        <v>1.184560034244873</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1643,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1706430925637629</v>
+        <v>0.1668788902685713</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1445626866695416</v>
+        <v>0.1474134437795191</v>
       </c>
       <c r="F35" t="n">
-        <v>6.542961534259433</v>
+        <v>8.57308309688292</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>758.455523620292</v>
+        <v>982.7743841027509</v>
       </c>
       <c r="I35" t="n">
-        <v>4444.689276460959</v>
+        <v>5889.147408165856</v>
       </c>
       <c r="J35" t="n">
-        <v>3.979701590754225</v>
+        <v>3.791619986570047</v>
       </c>
       <c r="K35" t="n">
-        <v>1.299002166859342</v>
+        <v>1.1888329810922</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1678,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1751903528754152</v>
+        <v>0.1542996333813425</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1500437172923487</v>
+        <v>0.1350791705036458</v>
       </c>
       <c r="F36" t="n">
-        <v>6.966751170219601</v>
+        <v>8.02788332222687</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>800.6819184054136</v>
+        <v>943.6896876792913</v>
       </c>
       <c r="I36" t="n">
-        <v>4570.35393367128</v>
+        <v>6115.955475714043</v>
       </c>
       <c r="J36" t="n">
-        <v>4.101329719933307</v>
+        <v>3.515333725878298</v>
       </c>
       <c r="K36" t="n">
-        <v>1.307048079872188</v>
+        <v>1.173719327203887</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1713,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1863756866969237</v>
+        <v>0.1540899076441313</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1621606773724275</v>
+        <v>0.1353750825920104</v>
       </c>
       <c r="F37" t="n">
-        <v>7.696701008840122</v>
+        <v>8.233574570694049</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>880.9781682547286</v>
+        <v>972.78524608267</v>
       </c>
       <c r="I37" t="n">
-        <v>4726.894284700011</v>
+        <v>6313.101623302319</v>
       </c>
       <c r="J37" t="n">
-        <v>4.467172730604004</v>
+        <v>3.549144589462195</v>
       </c>
       <c r="K37" t="n">
-        <v>1.306128967696965</v>
+        <v>1.17381688007669</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1748,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1817299536282213</v>
+        <v>0.1548012320083673</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1580805303226785</v>
+        <v>0.1365857413188926</v>
       </c>
       <c r="F38" t="n">
-        <v>7.684329181322112</v>
+        <v>8.498328957880538</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>888.1125665934284</v>
+        <v>1002.324976289845</v>
       </c>
       <c r="I38" t="n">
-        <v>4886.990553083545</v>
+        <v>6474.916015110702</v>
       </c>
       <c r="J38" t="n">
-        <v>4.290802557546684</v>
+        <v>3.555006373908159</v>
       </c>
       <c r="K38" t="n">
-        <v>1.273766146859278</v>
+        <v>1.168024052486736</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1783,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1813679770515466</v>
+        <v>0.1546038127262263</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1583726955080508</v>
+        <v>0.1368433886238362</v>
       </c>
       <c r="F39" t="n">
-        <v>7.887182277307045</v>
+        <v>8.70496176414051</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>908.2037946758132</v>
+        <v>1028.805652983378</v>
       </c>
       <c r="I39" t="n">
-        <v>5007.520122572094</v>
+        <v>6654.464950390295</v>
       </c>
       <c r="J39" t="n">
-        <v>4.276516950443937</v>
+        <v>3.51910271512698</v>
       </c>
       <c r="K39" t="n">
-        <v>1.248316254275815</v>
+        <v>1.163931299423554</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1818,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.188082169054524</v>
+        <v>0.1611949228350971</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1657767341384396</v>
+        <v>0.144076451872548</v>
       </c>
       <c r="F40" t="n">
-        <v>8.432122922602041</v>
+        <v>9.416432296304476</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>961.8776095737393</v>
+        <v>1105.940413652631</v>
       </c>
       <c r="I40" t="n">
-        <v>5114.135031561104</v>
+        <v>6860.888632230754</v>
       </c>
       <c r="J40" t="n">
-        <v>4.464449536444511</v>
+        <v>3.716122097954198</v>
       </c>
       <c r="K40" t="n">
-        <v>1.254473324319396</v>
+        <v>1.170556672300183</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1853,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1875804634848242</v>
+        <v>0.1684631825696061</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1658580159844184</v>
+        <v>0.1518987041347377</v>
       </c>
       <c r="F41" t="n">
-        <v>8.635328200531742</v>
+        <v>10.17014711522636</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>989.5230915970737</v>
+        <v>1193.720912748716</v>
       </c>
       <c r="I41" t="n">
-        <v>5275.192699783092</v>
+        <v>7085.945394955902</v>
       </c>
       <c r="J41" t="n">
-        <v>4.449181061574883</v>
+        <v>3.93910399076034</v>
       </c>
       <c r="K41" t="n">
-        <v>1.262199954381975</v>
+        <v>1.209996906930878</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1888,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1849168268801351</v>
+        <v>0.1673963963514767</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1636907025801385</v>
+        <v>0.1511978826618167</v>
       </c>
       <c r="F42" t="n">
-        <v>8.711756525432472</v>
+        <v>10.33405901050853</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>993.5090219948088</v>
+        <v>1210.069421159702</v>
       </c>
       <c r="I42" t="n">
-        <v>5372.734535612657</v>
+        <v>7228.76625503311</v>
       </c>
       <c r="J42" t="n">
-        <v>4.375313741341381</v>
+        <v>3.935827007940381</v>
       </c>
       <c r="K42" t="n">
-        <v>1.275738521897643</v>
+        <v>1.203586242557742</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1923,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1890949823707049</v>
+        <v>0.1682990525568038</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1684086298801617</v>
+        <v>0.1524872474723323</v>
       </c>
       <c r="F43" t="n">
-        <v>9.141049996955699</v>
+        <v>10.64388611279356</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1034.696433565156</v>
+        <v>1246.465138298091</v>
       </c>
       <c r="I43" t="n">
-        <v>5471.834422008724</v>
+        <v>7406.251665483311</v>
       </c>
       <c r="J43" t="n">
-        <v>4.458642330012155</v>
+        <v>3.921277704513857</v>
       </c>
       <c r="K43" t="n">
-        <v>1.27366801912998</v>
+        <v>1.22313649736261</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1958,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1863582871953975</v>
+        <v>0.1698499273985942</v>
       </c>
       <c r="E44" t="n">
-        <v>0.166118443593293</v>
+        <v>0.1544196286513562</v>
       </c>
       <c r="F44" t="n">
-        <v>9.207496404568067</v>
+        <v>11.00755923011515</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1041.125847101225</v>
+        <v>1278.427580900136</v>
       </c>
       <c r="I44" t="n">
-        <v>5586.689289591935</v>
+        <v>7526.806755118563</v>
       </c>
       <c r="J44" t="n">
-        <v>4.370042373374043</v>
+        <v>3.963245674288753</v>
       </c>
       <c r="K44" t="n">
-        <v>1.269889198149219</v>
+        <v>1.222347043318376</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1993,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.190632854535389</v>
+        <v>0.1707711738261899</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1709880209076072</v>
+        <v>0.1557489124824614</v>
       </c>
       <c r="F45" t="n">
-        <v>9.703968898255017</v>
+        <v>11.36787397840633</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1080.741557105266</v>
+        <v>1318.867479033089</v>
       </c>
       <c r="I45" t="n">
-        <v>5669.230310479549</v>
+        <v>7723.009975766909</v>
       </c>
       <c r="J45" t="n">
-        <v>4.43266451165555</v>
+        <v>3.951416131965656</v>
       </c>
       <c r="K45" t="n">
-        <v>1.234555982762907</v>
+        <v>1.222680619162573</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +2028,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1955521013250359</v>
+        <v>0.1708598622036208</v>
       </c>
       <c r="E46" t="n">
-        <v>0.176398579928013</v>
+        <v>0.1561587959306354</v>
       </c>
       <c r="F46" t="n">
-        <v>10.20972056634091</v>
+        <v>11.62227684923721</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1127.879482466792</v>
+        <v>1338.274964510552</v>
       </c>
       <c r="I46" t="n">
-        <v>5767.667413566132</v>
+        <v>7832.588340236835</v>
       </c>
       <c r="J46" t="n">
-        <v>4.58377454179599</v>
+        <v>3.918701158136713</v>
       </c>
       <c r="K46" t="n">
-        <v>1.248919890134363</v>
+        <v>1.210798396033679</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2063,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1914631234144956</v>
+        <v>0.1701452741036522</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1726599402380884</v>
+        <v>0.155738074001285</v>
       </c>
       <c r="F47" t="n">
-        <v>10.1824846154097</v>
+        <v>11.80973908148168</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1123.004033105776</v>
+        <v>1359.261003294246</v>
       </c>
       <c r="I47" t="n">
-        <v>5865.380304459997</v>
+        <v>7988.826080859505</v>
       </c>
       <c r="J47" t="n">
-        <v>4.480474852717253</v>
+        <v>3.897999990074954</v>
       </c>
       <c r="K47" t="n">
-        <v>1.235752193628493</v>
+        <v>1.224132048378224</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2098,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1897500027415846</v>
+        <v>0.174361031976995</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1713352300766207</v>
+        <v>0.1603195529289848</v>
       </c>
       <c r="F48" t="n">
-        <v>10.3042272741495</v>
+        <v>12.41756878893056</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1128.652080506234</v>
+        <v>1421.29743013641</v>
       </c>
       <c r="I48" t="n">
-        <v>5948.100470087027</v>
+        <v>8151.462594715167</v>
       </c>
       <c r="J48" t="n">
-        <v>4.398304647439809</v>
+        <v>3.936360727849944</v>
       </c>
       <c r="K48" t="n">
-        <v>1.230596785494211</v>
+        <v>1.212315826324959</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1907518279659292</v>
+        <v>0.1749439171015938</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1726882526973115</v>
+        <v>0.1611929823866205</v>
       </c>
       <c r="F49" t="n">
-        <v>10.56002619245192</v>
+        <v>12.72232911636885</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1155.571468517169</v>
+        <v>1450.177917622465</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.983720730425</v>
+        <v>8289.387488564778</v>
       </c>
       <c r="J49" t="n">
-        <v>4.4281495345876</v>
+        <v>3.858948096858507</v>
       </c>
       <c r="K49" t="n">
-        <v>1.229546439149446</v>
+        <v>1.197507442582169</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/SumRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5147587017934384</v>
+        <v>0.5743524216265981</v>
       </c>
       <c r="E2" t="n">
-        <v>0.245180202789793</v>
+        <v>0.3378815447524859</v>
       </c>
       <c r="F2" t="n">
-        <v>1.909494650708317</v>
+        <v>2.428850559607645</v>
       </c>
       <c r="G2" t="n">
-        <v>0.061</v>
+        <v>0.005</v>
       </c>
       <c r="H2" t="n">
-        <v>160.1181177351012</v>
+        <v>192.3716892415187</v>
       </c>
       <c r="I2" t="n">
-        <v>311.0547081132261</v>
+        <v>334.9366730216117</v>
       </c>
       <c r="J2" t="n">
-        <v>8.956190969726547</v>
+        <v>7.672712583149693</v>
       </c>
       <c r="K2" t="n">
-        <v>3.481990327321756</v>
+        <v>1.946921237931268</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4618881023525475</v>
+        <v>0.3634485264433324</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2825174698033968</v>
+        <v>0.1512647019244432</v>
       </c>
       <c r="F3" t="n">
-        <v>2.57504863415131</v>
+        <v>1.712894596312534</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003</v>
+        <v>0.031</v>
       </c>
       <c r="H3" t="n">
-        <v>194.3602890317141</v>
+        <v>159.0842947499114</v>
       </c>
       <c r="I3" t="n">
-        <v>420.7951840321789</v>
+        <v>437.7079095812906</v>
       </c>
       <c r="J3" t="n">
-        <v>7.171770335410962</v>
+        <v>4.577372985471129</v>
       </c>
       <c r="K3" t="n">
-        <v>2.117605628966524</v>
+        <v>1.909391712467203</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3385921314884081</v>
+        <v>0.2848440375495106</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1811140675570766</v>
+        <v>0.1145688083946321</v>
       </c>
       <c r="F4" t="n">
-        <v>2.150090768426338</v>
+        <v>1.672844834584971</v>
       </c>
       <c r="G4" t="n">
-        <v>0.005</v>
+        <v>0.033</v>
       </c>
       <c r="H4" t="n">
-        <v>196.7483119398033</v>
+        <v>141.2564962872542</v>
       </c>
       <c r="I4" t="n">
-        <v>581.0776259770794</v>
+        <v>495.908208233783</v>
       </c>
       <c r="J4" t="n">
-        <v>5.107108175526919</v>
+        <v>3.150284836723692</v>
       </c>
       <c r="K4" t="n">
-        <v>2.122914290111254</v>
+        <v>1.526432832135278</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3187459248023032</v>
+        <v>0.2352042785263464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.197093411374143</v>
+        <v>0.09863361397747961</v>
       </c>
       <c r="F5" t="n">
-        <v>2.620134313875342</v>
+        <v>1.722216694949062</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002</v>
+        <v>0.024</v>
       </c>
       <c r="H5" t="n">
-        <v>223.8963206603861</v>
+        <v>156.4848743538109</v>
       </c>
       <c r="I5" t="n">
-        <v>702.4288100287212</v>
+        <v>665.3147439929851</v>
       </c>
       <c r="J5" t="n">
-        <v>4.128371768596845</v>
+        <v>2.471974442534591</v>
       </c>
       <c r="K5" t="n">
-        <v>1.966191696689044</v>
+        <v>1.239535918931704</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2430221622433429</v>
+        <v>0.2107222603915608</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1317018919850109</v>
+        <v>0.09465200456679035</v>
       </c>
       <c r="F6" t="n">
-        <v>2.183089941116573</v>
+        <v>1.815471663211331</v>
       </c>
       <c r="G6" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="H6" t="n">
-        <v>192.1938514716771</v>
+        <v>169.6799827880859</v>
       </c>
       <c r="I6" t="n">
-        <v>790.8490719427871</v>
+        <v>805.2304605730275</v>
       </c>
       <c r="J6" t="n">
-        <v>3.255084905864639</v>
+        <v>2.362353871700868</v>
       </c>
       <c r="K6" t="n">
-        <v>1.773737763539221</v>
+        <v>1.243307680909876</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2077666457632025</v>
+        <v>0.2057616310824892</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1087374764836028</v>
+        <v>0.1064818349678004</v>
       </c>
       <c r="F7" t="n">
-        <v>2.09803482423035</v>
+        <v>2.072542844918736</v>
       </c>
       <c r="G7" t="n">
-        <v>0.006</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>194.7357432010168</v>
+        <v>201.4144641068252</v>
       </c>
       <c r="I7" t="n">
-        <v>937.2810659077712</v>
+        <v>978.8728007607924</v>
       </c>
       <c r="J7" t="n">
-        <v>2.908637671542315</v>
+        <v>2.377609772372137</v>
       </c>
       <c r="K7" t="n">
-        <v>1.486970907301779</v>
+        <v>1.300460891516176</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1923887742986801</v>
+        <v>0.1963387741816766</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1046049454181018</v>
+        <v>0.1089842931144676</v>
       </c>
       <c r="F8" t="n">
-        <v>2.191619763594582</v>
+        <v>2.247609645011992</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>223.0659753246838</v>
+        <v>231.4772597258436</v>
       </c>
       <c r="I8" t="n">
-        <v>1159.454215235957</v>
+        <v>1178.96865094845</v>
       </c>
       <c r="J8" t="n">
-        <v>3.150722392126704</v>
+        <v>2.651212360952822</v>
       </c>
       <c r="K8" t="n">
-        <v>1.463228472907605</v>
+        <v>1.264366089275006</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1896100590229962</v>
+        <v>0.189828863718354</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1116879493136688</v>
+        <v>0.1119277929220417</v>
       </c>
       <c r="F9" t="n">
-        <v>2.433328098152094</v>
+        <v>2.4367940232131</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>246.7926940076895</v>
+        <v>247.4336961951468</v>
       </c>
       <c r="I9" t="n">
-        <v>1301.580176069447</v>
+        <v>1303.456657477865</v>
       </c>
       <c r="J9" t="n">
-        <v>3.24620038613105</v>
+        <v>2.60606879386663</v>
       </c>
       <c r="K9" t="n">
-        <v>1.575881546700178</v>
+        <v>1.24582039677947</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1973484266402454</v>
+        <v>0.17709721906727</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1293271068639951</v>
+        <v>0.1073596952594116</v>
       </c>
       <c r="F10" t="n">
-        <v>2.901273119801324</v>
+        <v>2.539482467935198</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>302.1893618734298</v>
+        <v>262.4870204869547</v>
       </c>
       <c r="I10" t="n">
-        <v>1531.247889927713</v>
+        <v>1482.163423397685</v>
       </c>
       <c r="J10" t="n">
-        <v>3.351606621551049</v>
+        <v>2.376382777153394</v>
       </c>
       <c r="K10" t="n">
-        <v>1.635293375666821</v>
+        <v>1.233005559876652</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1817869856104005</v>
+        <v>0.1838277833278231</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1188475229650467</v>
+        <v>0.1210453051222711</v>
       </c>
       <c r="F11" t="n">
-        <v>2.888283089334891</v>
+        <v>2.928010944804766</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>297.5538942650571</v>
+        <v>311.0628864212497</v>
       </c>
       <c r="I11" t="n">
-        <v>1636.827263876657</v>
+        <v>1692.142943738413</v>
       </c>
       <c r="J11" t="n">
-        <v>3.106340858580024</v>
+        <v>2.89987073117624</v>
       </c>
       <c r="K11" t="n">
-        <v>1.587370365693271</v>
+        <v>1.231829222069464</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1768647984297352</v>
+        <v>0.1850127793283178</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1188975307135195</v>
+        <v>0.1276193130838331</v>
       </c>
       <c r="F12" t="n">
-        <v>3.051114972256297</v>
+        <v>3.2235860880087</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>314.1445056850122</v>
+        <v>342.9821331474391</v>
       </c>
       <c r="I12" t="n">
-        <v>1776.184455437668</v>
+        <v>1853.829418662989</v>
       </c>
       <c r="J12" t="n">
-        <v>3.067690139229773</v>
+        <v>2.948456190139461</v>
       </c>
       <c r="K12" t="n">
-        <v>1.555455120678307</v>
+        <v>1.177637162003847</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.16896822992055</v>
+        <v>0.1711698404510132</v>
       </c>
       <c r="E13" t="n">
-        <v>0.115005127967339</v>
+        <v>0.1173497002205595</v>
       </c>
       <c r="F13" t="n">
-        <v>3.131180821796618</v>
+        <v>3.180404950973318</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>331.9638178719993</v>
+        <v>339.6321609263122</v>
       </c>
       <c r="I13" t="n">
-        <v>1964.652278289776</v>
+        <v>1984.182260329389</v>
       </c>
       <c r="J13" t="n">
-        <v>2.919451804538109</v>
+        <v>2.730340280495358</v>
       </c>
       <c r="K13" t="n">
-        <v>1.565447140152733</v>
+        <v>1.173884808685491</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1544863276619849</v>
+        <v>0.1528920416358371</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1035517690874056</v>
+        <v>0.1018614417343815</v>
       </c>
       <c r="F14" t="n">
-        <v>3.03303556534771</v>
+        <v>2.996085523805022</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>329.5219445844546</v>
+        <v>328.3936867166379</v>
       </c>
       <c r="I14" t="n">
-        <v>2133.016879690781</v>
+        <v>2147.879531223842</v>
       </c>
       <c r="J14" t="n">
-        <v>2.735826454424792</v>
+        <v>2.465968803877272</v>
       </c>
       <c r="K14" t="n">
-        <v>1.508829584936505</v>
+        <v>1.147922797393239</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.145246836784274</v>
+        <v>0.1357646332644794</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09776054993895589</v>
+        <v>0.08775155733472828</v>
       </c>
       <c r="F15" t="n">
-        <v>3.058711186608488</v>
+        <v>2.827659562222575</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>330.3110299114203</v>
+        <v>318.9393172141644</v>
       </c>
       <c r="I15" t="n">
-        <v>2274.135789972559</v>
+        <v>2349.207665834794</v>
       </c>
       <c r="J15" t="n">
-        <v>2.585180407528967</v>
+        <v>2.162719060622105</v>
       </c>
       <c r="K15" t="n">
-        <v>1.531332718794198</v>
+        <v>1.116926416829792</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1417379508062178</v>
+        <v>0.1324840324945657</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09703680241070844</v>
+        <v>0.08730090918699096</v>
       </c>
       <c r="F16" t="n">
-        <v>3.170789921371602</v>
+        <v>2.932157469343325</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>346.1892613529878</v>
+        <v>329.0342956388284</v>
       </c>
       <c r="I16" t="n">
-        <v>2442.459901415486</v>
+        <v>2483.576997494585</v>
       </c>
       <c r="J16" t="n">
-        <v>2.499569380849095</v>
+        <v>2.120719475604643</v>
       </c>
       <c r="K16" t="n">
-        <v>1.472524822221151</v>
+        <v>1.10587757120634</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1405666541727946</v>
+        <v>0.1365893912552868</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09843756859302955</v>
+        <v>0.09426534180701651</v>
       </c>
       <c r="F17" t="n">
-        <v>3.336570263473989</v>
+        <v>3.22722879865809</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>356.6716124784796</v>
+        <v>364.0492017564865</v>
       </c>
       <c r="I17" t="n">
-        <v>2537.384236520515</v>
+        <v>2665.281676789051</v>
       </c>
       <c r="J17" t="n">
-        <v>2.41724553427446</v>
+        <v>2.205589883084559</v>
       </c>
       <c r="K17" t="n">
-        <v>1.459079278275009</v>
+        <v>1.109878854394357</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1519055595032549</v>
+        <v>0.1397106239232981</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1126419279987759</v>
+        <v>0.09988241206789517</v>
       </c>
       <c r="F18" t="n">
-        <v>3.868861684022439</v>
+        <v>3.507830691232645</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>437.6406726015339</v>
+        <v>394.0759113340508</v>
       </c>
       <c r="I18" t="n">
-        <v>2881.004974621463</v>
+        <v>2820.658159471113</v>
       </c>
       <c r="J18" t="n">
-        <v>2.980866887398515</v>
+        <v>2.285758285019376</v>
       </c>
       <c r="K18" t="n">
-        <v>1.371381242818427</v>
+        <v>1.114915639721085</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1605233277105302</v>
+        <v>0.1513164920874304</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1237041754171325</v>
+        <v>0.1140935312140722</v>
       </c>
       <c r="F19" t="n">
-        <v>4.359777933815017</v>
+        <v>4.065138520340883</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>494.1821347291203</v>
+        <v>468.4737839972426</v>
       </c>
       <c r="I19" t="n">
-        <v>3078.568964258409</v>
+        <v>3095.9862836799</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3399913588364</v>
+        <v>2.757928855136728</v>
       </c>
       <c r="K19" t="n">
-        <v>1.394160381148344</v>
+        <v>1.099340963466015</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1482539135397079</v>
+        <v>0.1562546934994103</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1130577942644891</v>
+        <v>0.1213891849663281</v>
       </c>
       <c r="F20" t="n">
-        <v>4.212223295995375</v>
+        <v>4.481641027869929</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>482.3148646215104</v>
+        <v>516.204291251608</v>
       </c>
       <c r="I20" t="n">
-        <v>3253.302750030464</v>
+        <v>3303.608228917335</v>
       </c>
       <c r="J20" t="n">
-        <v>3.058564197126362</v>
+        <v>3.060416801974541</v>
       </c>
       <c r="K20" t="n">
-        <v>1.361188245001207</v>
+        <v>1.098354570041856</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1606482326385549</v>
+        <v>0.1599111286714315</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1276028874668446</v>
+        <v>0.1268367636584957</v>
       </c>
       <c r="F21" t="n">
-        <v>4.86144816475039</v>
+        <v>4.834896410222491</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>555.9845322559945</v>
+        <v>559.2851171977692</v>
       </c>
       <c r="I21" t="n">
-        <v>3460.881723528905</v>
+        <v>3497.474640097934</v>
       </c>
       <c r="J21" t="n">
-        <v>3.439784126996339</v>
+        <v>3.140777966304749</v>
       </c>
       <c r="K21" t="n">
-        <v>1.382496111856729</v>
+        <v>1.128291004264646</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1534813844956585</v>
+        <v>0.15174363047492</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1216573763939915</v>
+        <v>0.119854293274729</v>
       </c>
       <c r="F22" t="n">
-        <v>4.82281754093756</v>
+        <v>4.758444163399268</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>553.7864986034008</v>
+        <v>563.8672707881335</v>
       </c>
       <c r="I22" t="n">
-        <v>3608.167208180648</v>
+        <v>3715.920523473498</v>
       </c>
       <c r="J22" t="n">
-        <v>3.236328151649229</v>
+        <v>3.079752237776302</v>
       </c>
       <c r="K22" t="n">
-        <v>1.318518790179633</v>
+        <v>1.157396976208533</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1591167856497036</v>
+        <v>0.1510320086427121</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1288691880112037</v>
+        <v>0.120493591687414</v>
       </c>
       <c r="F23" t="n">
-        <v>5.260476800550133</v>
+        <v>4.945639744974061</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>606.8796161236658</v>
+        <v>585.3381257120049</v>
       </c>
       <c r="I23" t="n">
-        <v>3814.051507172313</v>
+        <v>3875.589889668396</v>
       </c>
       <c r="J23" t="n">
-        <v>3.393096436247743</v>
+        <v>3.169321533046188</v>
       </c>
       <c r="K23" t="n">
-        <v>1.273872516749853</v>
+        <v>1.186348797215217</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1575361066806408</v>
+        <v>0.1511365647476639</v>
       </c>
       <c r="E24" t="n">
-        <v>0.128485627600663</v>
+        <v>0.1218654118079281</v>
       </c>
       <c r="F24" t="n">
-        <v>5.422840230859307</v>
+        <v>5.163328040368897</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>621.6884810086856</v>
+        <v>610.2238385834758</v>
       </c>
       <c r="I24" t="n">
-        <v>3946.323760996457</v>
+        <v>4037.565890175546</v>
       </c>
       <c r="J24" t="n">
-        <v>3.320052789301816</v>
+        <v>3.178335929181483</v>
       </c>
       <c r="K24" t="n">
-        <v>1.252246579166379</v>
+        <v>1.267798638309526</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1605410242692418</v>
+        <v>0.1586205997106896</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1329272421728352</v>
+        <v>0.1309436457538043</v>
       </c>
       <c r="F25" t="n">
-        <v>5.813800648848229</v>
+        <v>5.731143678519924</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>665.3668770238741</v>
+        <v>686.8106901324071</v>
       </c>
       <c r="I25" t="n">
-        <v>4144.528665196465</v>
+        <v>4329.895936499363</v>
       </c>
       <c r="J25" t="n">
-        <v>3.426476175230086</v>
+        <v>3.454395783148567</v>
       </c>
       <c r="K25" t="n">
-        <v>1.255878983410537</v>
+        <v>1.278498915009699</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.156177827060109</v>
+        <v>0.1535065275007688</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1294745937392265</v>
+        <v>0.1267187593837047</v>
       </c>
       <c r="F26" t="n">
-        <v>5.84864855814947</v>
+        <v>5.730470968314174</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>678.3657769014803</v>
+        <v>692.4216174862714</v>
       </c>
       <c r="I26" t="n">
-        <v>4343.547286263587</v>
+        <v>4510.698201304849</v>
       </c>
       <c r="J26" t="n">
-        <v>3.314020972045142</v>
+        <v>3.341721857796484</v>
       </c>
       <c r="K26" t="n">
-        <v>1.23478078380374</v>
+        <v>1.246589093356956</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1415131641727738</v>
+        <v>0.1533129443346608</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1153397850316998</v>
+        <v>0.1274993145887663</v>
       </c>
       <c r="F27" t="n">
-        <v>5.406759418033902</v>
+        <v>5.939224581891444</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>633.3594098475772</v>
+        <v>709.3721556480966</v>
       </c>
       <c r="I27" t="n">
-        <v>4475.621851507095</v>
+        <v>4626.955399797399</v>
       </c>
       <c r="J27" t="n">
-        <v>2.949133506500223</v>
+        <v>3.357133779702806</v>
       </c>
       <c r="K27" t="n">
-        <v>1.214409525824159</v>
+        <v>1.234114868261268</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1432101660244682</v>
+        <v>0.1502959325314489</v>
       </c>
       <c r="E28" t="n">
-        <v>0.118010465025188</v>
+        <v>0.1253046364294327</v>
       </c>
       <c r="F28" t="n">
-        <v>5.683010525742271</v>
+        <v>6.013931086964452</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>659.618290419342</v>
+        <v>722.564447476006</v>
       </c>
       <c r="I28" t="n">
-        <v>4605.945993433474</v>
+        <v>4807.611458978187</v>
       </c>
       <c r="J28" t="n">
-        <v>2.943601020497089</v>
+        <v>3.395881410611048</v>
       </c>
       <c r="K28" t="n">
-        <v>1.218890923111386</v>
+        <v>1.263013055175861</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1325927243137736</v>
+        <v>0.1471758521264095</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1079504721635969</v>
+        <v>0.1229478933800008</v>
       </c>
       <c r="F29" t="n">
-        <v>5.380706418622615</v>
+        <v>6.074628641516261</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>627.1490940114377</v>
+        <v>731.2817304268322</v>
       </c>
       <c r="I29" t="n">
-        <v>4729.890702956843</v>
+        <v>4968.761653907283</v>
       </c>
       <c r="J29" t="n">
-        <v>2.711216381665019</v>
+        <v>3.315709638830148</v>
       </c>
       <c r="K29" t="n">
-        <v>1.181035782567216</v>
+        <v>1.25393991386096</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1356336330042883</v>
+        <v>0.1460974502330437</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1120170656000339</v>
+        <v>0.1227667794743837</v>
       </c>
       <c r="F30" t="n">
-        <v>5.74315609388071</v>
+        <v>6.262033858534243</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>667.4450314428525</v>
+        <v>755.3548256218469</v>
       </c>
       <c r="I30" t="n">
-        <v>4920.940453034609</v>
+        <v>5170.212241329067</v>
       </c>
       <c r="J30" t="n">
-        <v>2.795186401438425</v>
+        <v>3.267485751356922</v>
       </c>
       <c r="K30" t="n">
-        <v>1.17054023221836</v>
+        <v>1.318640456559684</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1540806599036129</v>
+        <v>0.145148881853762</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1317018413825444</v>
+        <v>0.1225337729080942</v>
       </c>
       <c r="F31" t="n">
-        <v>6.885111461918972</v>
+        <v>6.418226071891988</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>797.2703050217228</v>
+        <v>764.2243415700589</v>
       </c>
       <c r="I31" t="n">
-        <v>5174.369745823165</v>
+        <v>5265.106639540067</v>
       </c>
       <c r="J31" t="n">
-        <v>3.367422351129779</v>
+        <v>3.214299653865496</v>
       </c>
       <c r="K31" t="n">
-        <v>1.222576898122977</v>
+        <v>1.29590561001781</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1539836050417257</v>
+        <v>0.1469848043688286</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1322908769658726</v>
+        <v>0.1251126198654654</v>
       </c>
       <c r="F32" t="n">
-        <v>7.098397421628557</v>
+        <v>6.720170285058918</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>822.1683471147162</v>
+        <v>796.3292399315295</v>
       </c>
       <c r="I32" t="n">
-        <v>5339.3239292711</v>
+        <v>5417.765757154749</v>
       </c>
       <c r="J32" t="n">
-        <v>3.426675183845178</v>
+        <v>3.290424862321594</v>
       </c>
       <c r="K32" t="n">
-        <v>1.188548367318493</v>
+        <v>1.307707953202108</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1552958135032351</v>
+        <v>0.1475957303477659</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1342832715505793</v>
+        <v>0.126391644038009</v>
       </c>
       <c r="F33" t="n">
-        <v>7.390624792237798</v>
+        <v>6.96072107006326</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>842.1866452319721</v>
+        <v>820.7497889021961</v>
       </c>
       <c r="I33" t="n">
-        <v>5423.112357207412</v>
+        <v>5560.79628433926</v>
       </c>
       <c r="J33" t="n">
-        <v>3.392038663387215</v>
+        <v>3.275645641854085</v>
       </c>
       <c r="K33" t="n">
-        <v>1.17927797941213</v>
+        <v>1.290779083746895</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.165689134729284</v>
+        <v>0.1489559815868347</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1455366983700878</v>
+        <v>0.1283993627845842</v>
       </c>
       <c r="F34" t="n">
-        <v>8.22179173654485</v>
+        <v>7.246132402403074</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>938.7177282839104</v>
+        <v>852.2256962494297</v>
       </c>
       <c r="I34" t="n">
-        <v>5665.535822959435</v>
+        <v>5721.325771349572</v>
       </c>
       <c r="J34" t="n">
-        <v>3.742755387772072</v>
+        <v>3.31550742994889</v>
       </c>
       <c r="K34" t="n">
-        <v>1.184560034244873</v>
+        <v>1.301107825001389</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1668788902685713</v>
+        <v>0.1514606043332083</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1474134437795191</v>
+        <v>0.1316349175185636</v>
       </c>
       <c r="F35" t="n">
-        <v>8.57308309688292</v>
+        <v>7.639614493523057</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>982.7743841027509</v>
+        <v>902.6584102864501</v>
       </c>
       <c r="I35" t="n">
-        <v>5889.147408165856</v>
+        <v>5959.691064619228</v>
       </c>
       <c r="J35" t="n">
-        <v>3.791619986570047</v>
+        <v>3.403098319043004</v>
       </c>
       <c r="K35" t="n">
-        <v>1.1888329810922</v>
+        <v>1.310153652327017</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1542996333813425</v>
+        <v>0.1490887028365905</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1350791705036458</v>
+        <v>0.1297498097192403</v>
       </c>
       <c r="F36" t="n">
-        <v>8.02788332222687</v>
+        <v>7.709267636565666</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>943.6896876792913</v>
+        <v>915.4029231216153</v>
       </c>
       <c r="I36" t="n">
-        <v>6115.955475714043</v>
+        <v>6139.988514924218</v>
       </c>
       <c r="J36" t="n">
-        <v>3.515333725878298</v>
+        <v>3.34877132953595</v>
       </c>
       <c r="K36" t="n">
-        <v>1.173719327203887</v>
+        <v>1.302951269653025</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1540899076441313</v>
+        <v>0.1481774044193671</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1353750825920104</v>
+        <v>0.129331771773778</v>
       </c>
       <c r="F37" t="n">
-        <v>8.233574570694049</v>
+        <v>7.862691967204805</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>972.78524608267</v>
+        <v>927.1726050578226</v>
       </c>
       <c r="I37" t="n">
-        <v>6313.101623302319</v>
+        <v>6257.179417408121</v>
       </c>
       <c r="J37" t="n">
-        <v>3.549144589462195</v>
+        <v>3.281343903440082</v>
       </c>
       <c r="K37" t="n">
-        <v>1.17381688007669</v>
+        <v>1.31325249586403</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1548012320083673</v>
+        <v>0.15495927661582</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1365857413188926</v>
+        <v>0.1367471920601264</v>
       </c>
       <c r="F38" t="n">
-        <v>8.498328957880538</v>
+        <v>8.508596374124346</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>1002.324976289845</v>
+        <v>1010.357846502827</v>
       </c>
       <c r="I38" t="n">
-        <v>6474.916015110702</v>
+        <v>6520.150768435367</v>
       </c>
       <c r="J38" t="n">
-        <v>3.555006373908159</v>
+        <v>3.520968990548829</v>
       </c>
       <c r="K38" t="n">
-        <v>1.168024052486736</v>
+        <v>1.316775982345484</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1546038127262263</v>
+        <v>0.15909396305483</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1368433886238362</v>
+        <v>0.1414278698416962</v>
       </c>
       <c r="F39" t="n">
-        <v>8.70496176414051</v>
+        <v>9.005610982316782</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>1028.805652983378</v>
+        <v>1060.489973062284</v>
       </c>
       <c r="I39" t="n">
-        <v>6654.464950390295</v>
+        <v>6665.809014367174</v>
       </c>
       <c r="J39" t="n">
-        <v>3.51910271512698</v>
+        <v>3.630835820848276</v>
       </c>
       <c r="K39" t="n">
-        <v>1.163931299423554</v>
+        <v>1.313513449966548</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1611949228350971</v>
+        <v>0.1651655082755216</v>
       </c>
       <c r="E40" t="n">
-        <v>0.144076451872548</v>
+        <v>0.1481280696688996</v>
       </c>
       <c r="F40" t="n">
-        <v>9.416432296304476</v>
+        <v>9.694268727185674</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1105.940413652631</v>
+        <v>1138.55637609154</v>
       </c>
       <c r="I40" t="n">
-        <v>6860.888632230754</v>
+        <v>6893.427011360338</v>
       </c>
       <c r="J40" t="n">
-        <v>3.716122097954198</v>
+        <v>3.814633731379778</v>
       </c>
       <c r="K40" t="n">
-        <v>1.170556672300183</v>
+        <v>1.284878820565173</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1684631825696061</v>
+        <v>0.1718402559219052</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1518987041347377</v>
+        <v>0.1553430498645727</v>
       </c>
       <c r="F41" t="n">
-        <v>10.17014711522636</v>
+        <v>10.41632475976299</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1193.720912748716</v>
+        <v>1213.530249771269</v>
       </c>
       <c r="I41" t="n">
-        <v>7085.945394955902</v>
+        <v>7061.967193081765</v>
       </c>
       <c r="J41" t="n">
-        <v>3.93910399076034</v>
+        <v>3.934879955132038</v>
       </c>
       <c r="K41" t="n">
-        <v>1.209996906930878</v>
+        <v>1.293445218612437</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1673963963514767</v>
+        <v>0.1742515221502927</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1511978826618167</v>
+        <v>0.1581863766668354</v>
       </c>
       <c r="F42" t="n">
-        <v>10.33405901050853</v>
+        <v>10.84655737040935</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1210.069421159702</v>
+        <v>1261.385208056746</v>
       </c>
       <c r="I42" t="n">
-        <v>7228.76625503311</v>
+        <v>7238.876266279016</v>
       </c>
       <c r="J42" t="n">
-        <v>3.935827007940381</v>
+        <v>3.978738898084935</v>
       </c>
       <c r="K42" t="n">
-        <v>1.203586242557742</v>
+        <v>1.262863127159657</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1682990525568038</v>
+        <v>0.1721004428665114</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1524872474723323</v>
+        <v>0.156360907559791</v>
       </c>
       <c r="F43" t="n">
-        <v>10.64388611279356</v>
+        <v>10.93427725232965</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1246.465138298091</v>
+        <v>1272.333072229061</v>
       </c>
       <c r="I43" t="n">
-        <v>7406.251665483311</v>
+        <v>7392.968030976757</v>
       </c>
       <c r="J43" t="n">
-        <v>3.921277704513857</v>
+        <v>3.910079747434659</v>
       </c>
       <c r="K43" t="n">
-        <v>1.22313649736261</v>
+        <v>1.26124472445229</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1698499273985942</v>
+        <v>0.1733349698394316</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1544196286513562</v>
+        <v>0.1579694488327297</v>
       </c>
       <c r="F44" t="n">
-        <v>11.00755923011515</v>
+        <v>11.28077399808491</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1278.427580900136</v>
+        <v>1314.991945722949</v>
       </c>
       <c r="I44" t="n">
-        <v>7526.806755118563</v>
+        <v>7586.4203682678</v>
       </c>
       <c r="J44" t="n">
-        <v>3.963245674288753</v>
+        <v>3.942268480020092</v>
       </c>
       <c r="K44" t="n">
-        <v>1.222347043318376</v>
+        <v>1.265884045459562</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1707711738261899</v>
+        <v>0.1754511436560379</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1557489124824614</v>
+        <v>0.1605136643744443</v>
       </c>
       <c r="F45" t="n">
-        <v>11.36787397840633</v>
+        <v>11.74569954866715</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1318.867479033089</v>
+        <v>1367.278747697597</v>
       </c>
       <c r="I45" t="n">
-        <v>7723.009975766909</v>
+        <v>7792.931520458314</v>
       </c>
       <c r="J45" t="n">
-        <v>3.951416131965656</v>
+        <v>3.971421767800329</v>
       </c>
       <c r="K45" t="n">
-        <v>1.222680619162573</v>
+        <v>1.241343522659412</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1708598622036208</v>
+        <v>0.1755469130720607</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1561587959306354</v>
+        <v>0.1609289505378774</v>
       </c>
       <c r="F46" t="n">
-        <v>11.62227684923721</v>
+        <v>12.00898638654694</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1338.274964510552</v>
+        <v>1388.008949974858</v>
       </c>
       <c r="I46" t="n">
-        <v>7832.588340236835</v>
+        <v>7906.76933980087</v>
       </c>
       <c r="J46" t="n">
-        <v>3.918701158136713</v>
+        <v>3.954082431237655</v>
       </c>
       <c r="K46" t="n">
-        <v>1.210798396033679</v>
+        <v>1.207306135551852</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1701452741036522</v>
+        <v>0.1748344653426619</v>
       </c>
       <c r="E47" t="n">
-        <v>0.155738074001285</v>
+        <v>0.1605086748104164</v>
       </c>
       <c r="F47" t="n">
-        <v>11.80973908148168</v>
+        <v>12.20417574507548</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1359.261003294246</v>
+        <v>1409.760376323178</v>
       </c>
       <c r="I47" t="n">
-        <v>7988.826080859505</v>
+        <v>8063.40084925565</v>
       </c>
       <c r="J47" t="n">
-        <v>3.897999990074954</v>
+        <v>3.913688258149137</v>
       </c>
       <c r="K47" t="n">
-        <v>1.224132048378224</v>
+        <v>1.202730964328208</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.174361031976995</v>
+        <v>0.1784089641642243</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1603195529289848</v>
+        <v>0.1644363275003508</v>
       </c>
       <c r="F48" t="n">
-        <v>12.41756878893056</v>
+        <v>12.76845368959609</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1421.29743013641</v>
+        <v>1458.99496112919</v>
       </c>
       <c r="I48" t="n">
-        <v>8151.462594715167</v>
+        <v>8177.8119612095</v>
       </c>
       <c r="J48" t="n">
-        <v>3.936360727849944</v>
+        <v>3.917237596564771</v>
       </c>
       <c r="K48" t="n">
-        <v>1.212315826324959</v>
+        <v>1.203896230410752</v>
       </c>
     </row>
     <row r="49">
@@ -2136,28 +2136,28 @@
         <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1749439171015938</v>
+        <v>0.1802756201781706</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1611929823866205</v>
+        <v>0.1666135471811401</v>
       </c>
       <c r="F49" t="n">
-        <v>12.72232911636885</v>
+        <v>13.1953342818</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1450.177917622465</v>
+        <v>1503.501917632172</v>
       </c>
       <c r="I49" t="n">
-        <v>8289.387488564778</v>
+        <v>8340.018002135988</v>
       </c>
       <c r="J49" t="n">
-        <v>3.858948096858507</v>
+        <v>3.96370608929188</v>
       </c>
       <c r="K49" t="n">
-        <v>1.197507442582169</v>
+        <v>1.212199043754518</v>
       </c>
     </row>
   </sheetData>
